--- a/naver-place-crawler/results_nail/판교_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/판교_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>예쁘다그대 네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>ped7913@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1361-6532</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>http://www.instagram.com/yebbeudageudaenail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +602,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4wl1y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1157</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1252</v>
+        <v>13</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1048880915</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1048880915</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일샾</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aisru33@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1410-5599</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로925번길 19 3층 309호 네일샾</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mxgxkQxj</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -710,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="Q3" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R3" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1077097098</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077097098</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>031-702-8870</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,19 +781,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ui8r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1369</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="n">
-        <v>567</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1936</v>
+        <v>152</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +880,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4oct0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2430</v>
+        <v>315</v>
       </c>
       <c r="Q5" t="n">
-        <v>2338</v>
+        <v>33</v>
       </c>
       <c r="R5" t="n">
-        <v>4768</v>
+        <v>348</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>쏘햅삐네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>ssohapbbi_nail@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1317-6311</t>
+          <t>0507-1365-1459</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://www.instagram.com/ssohapbbi_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -994,14 +974,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wtlgb2g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>456</v>
+        <v>340</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1699230267</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1699230267</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,24 +1026,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>더다인</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>clarkjenny@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>0507-1448-2080</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1068,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4u9e4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>201</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>333</v>
+        <v>7</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>37870367</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/37870367</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1120,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1196,7 +1168,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>395</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="R8" t="n">
-        <v>152</v>
+        <v>464</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>바비앤네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>rladbrud8791@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1418-0917</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 운중로 176</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>http://barbienail.itpage.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1251,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs4bo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1938</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>638</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>2576</v>
+        <v>9</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>21733065</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/21733065</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1340,34 +1308,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>orosy2020@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1393,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>120</v>
+        <v>1031</v>
       </c>
       <c r="Q10" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R10" t="n">
-        <v>232</v>
+        <v>1152</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
+          <t>네일탐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nailpalace@naver.com</t>
+          <t>kangjooho0519@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>0507-1344-3330</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 \u002F 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1476,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc34mh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>344</v>
+        <v>26</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>1400616486</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/1400616486</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1532,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>이엘르</t>
+          <t>팜네일유카리</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tti_eun@naver.com</t>
+          <t>micchudog@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1402-5003</t>
+          <t>0507-1387-4579</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 장미로48번길 14 엔즈빌오피스텔 2층 223호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tti_eun</t>
+          <t>https://www.instagram.com/palm_nail_yukari</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1569,22 +1533,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46qbd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1593,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>284</v>
+        <v>5</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1682567809</t>
+          <t>1434919594</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682567809</t>
+          <t>https://m.place.naver.com/place/1434919594</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1630,25 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>바이뮤즈</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1436-7943</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 정자일로 121 1층 C 10-1</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bymuse_</t>
+          <t>https://www.instagram.com/nail.suda</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1668,14 +1632,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4nsdt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1687,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>443</v>
+        <v>88</v>
       </c>
       <c r="Q13" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
-        <v>500</v>
+        <v>188</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1702,17 +1662,5907 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1198012559</t>
+          <t>37851165</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198012559</t>
+          <t>https://m.place.naver.com/place/37851165</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>라모르뷰티 분당수내 본점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lamour11@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1465-5979</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lamour.nail</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>81</v>
+      </c>
+      <c r="R14" t="n">
+        <v>343</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1397181784</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397181784</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HENA BEAUTY LAB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>amyloves_red@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1419-0757</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_zLygn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>597</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+      <c r="R15" t="n">
+        <v>847</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>30844297</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30844297</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>네일팰리스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nailpalace@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1325-7941</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailpalace_official/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>101</v>
+      </c>
+      <c r="R16" t="n">
+        <v>344</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>33928799</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33928799</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>트리나네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>treenanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/tree_na_nail</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1157</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1252</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1331495059</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331495059</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>레푸스 판교점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yedamcp@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>031-702-8870</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yedamcp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1373</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>567</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1710320799</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710320799</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>네일바니</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>suna8457@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1305-2049</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail6unny</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>136</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1519571633</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1519571633</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>네일설렘</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mistymoon5@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1436-0914</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailseolrem</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>39</v>
+      </c>
+      <c r="R20" t="n">
+        <v>400</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1622892642</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1622892642</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tykd2048@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1466-3338</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dada.nail/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>70</v>
+      </c>
+      <c r="R21" t="n">
+        <v>511</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>240537974</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/240537974</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>손 꽃처럼예쁘다</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kshkjs1225@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1355-4142</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>66</v>
+      </c>
+      <c r="R22" t="n">
+        <v>78</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1207469718</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1207469718</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>포세타네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>achellnet@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailfossetta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>86</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1702940792</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702940792</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>손끝에담다</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cc850625@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1429-4102</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sondam41</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>16</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>199302625</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/199302625</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>반디인하우스 큐릭스 분당서현점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sdfw3t4@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1359-2111</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sdfw3t4</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1105</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>34</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1139</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1557758291</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1557758291</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>내일그리고네일</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>major13564@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1397-7847</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tomorrow7836</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47</v>
+      </c>
+      <c r="R26" t="n">
+        <v>564</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1389203098</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389203098</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>포쉬네일 AK분당점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>woosy0225@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1416-2324</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/forsynail_footcare</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>683</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>58</v>
+      </c>
+      <c r="R27" t="n">
+        <v>741</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1692272902</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692272902</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>꼼앤네일아트 속눈썹 서현역점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ujin9132@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1403-8660</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 1동 2층 205호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ccom_heewon</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22</v>
+      </c>
+      <c r="R28" t="n">
+        <v>154</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1495049038</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1495049038</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>퀸즈</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mam-hand@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1363-4230</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1429117837</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1429117837</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>네일온</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dlgksmf3595@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1491-7802</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailon7793</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>316</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1655818723</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1655818723</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>네일 조안</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lds9525@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1369-6361</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>31</v>
+      </c>
+      <c r="R31" t="n">
+        <v>359</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1520161470</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1520161470</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>버베인네일 분당수내점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>llltwjhlll@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1375-0335</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/llltwjhlll</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>31</v>
+      </c>
+      <c r="R32" t="n">
+        <v>84</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2016496556</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2016496556</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>디네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>b_ye_bye@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1498-4179</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://instagram.com/d.nail_4179</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>111</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1139274960</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1139274960</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>예스네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lovmaria@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1320-2494</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/ye_s_nail</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>660</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>13</v>
+      </c>
+      <c r="R34" t="n">
+        <v>673</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1073307347</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073307347</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>백프로네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dodream8069@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1416-7323</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_MgAwxl</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>118</v>
+      </c>
+      <c r="R35" t="n">
+        <v>184</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>512636239</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/512636239</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>이마네일</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pdr0613@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1427-8952</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_yxlBPj</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R36" t="n">
+        <v>71</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1053041064</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053041064</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>로코코네일 판교본점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nail_rococo@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1315-1583</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/rococonail</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>133</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1008417568</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1008417568</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>후와네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kimnk980409@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1342-1792</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>446</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>18</v>
+      </c>
+      <c r="R38" t="n">
+        <v>464</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1782262137</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782262137</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>수요일네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>loosetime@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1333-9913</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1865078719</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1865078719</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>그리너리프라이빗뷰티샵</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q19900320@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1446-1041</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/greenery_nail/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>69</v>
+      </c>
+      <c r="R40" t="n">
+        <v>306</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>50639356</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/50639356</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>메종드리엘</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>lovelyzzzzzzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1363-0109</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>39</v>
+      </c>
+      <c r="R41" t="n">
+        <v>43</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1572212961</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572212961</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>iam_jihye@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbylala.official</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>29</v>
+      </c>
+      <c r="R42" t="n">
+        <v>386</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1737395332</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1737395332</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>uijn_dd@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1078</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>524</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1602</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>36524000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36524000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>헤몬네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>barbie7085055@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbie7085055</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1297</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>718</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1117775011</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117775011</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>달래네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>w130312@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1471-1290</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dalraenail</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>211</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1453685923</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1453685923</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cxd1000@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1305-3099</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/harr__nail/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>36</v>
+      </c>
+      <c r="R46" t="n">
+        <v>306</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2066713618</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066713618</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>위치네일스 판교점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>witch_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>031-622-7290</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/witch_nail</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>554</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>67</v>
+      </c>
+      <c r="R47" t="n">
+        <v>621</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1458353971</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1458353971</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>네일그자체</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wisp1205@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_itself</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23</v>
+      </c>
+      <c r="R48" t="n">
+        <v>189</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2089755300</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089755300</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>라온네일클리닉 판교 본점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1418-3314</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sungunara226</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>283</v>
+      </c>
+      <c r="R49" t="n">
+        <v>350</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1137420501</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137420501</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>휘우네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jess778@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1491-7588</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_eFEVn/chat</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>13</v>
+      </c>
+      <c r="R50" t="n">
+        <v>307</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1758546666</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758546666</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>숨숨네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rnys11@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1334-7410</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soomsoom.nail</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>12</v>
+      </c>
+      <c r="R51" t="n">
+        <v>223</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1619651823</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1619651823</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일아르떼</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>tpfla1999@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__nail.arte/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>37</v>
+      </c>
+      <c r="R52" t="n">
+        <v>510</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1010349043</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010349043</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>포쉬네일 판교아브뉴프랑점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>silentforest_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>031-603-3011</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>132</v>
+      </c>
+      <c r="R53" t="n">
+        <v>333</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>38258395</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38258395</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>이브네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>am7734@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1405-0716</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/evenail_dj_hs</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>23</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1345933789</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1345933789</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>모아나네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7daystaste@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://instagram.com/moana.jy</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1078179761</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1078179761</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>네일오브윤 분당점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>o___o373@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1366-7390</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/o___o373</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1158</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>916</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2074</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1300308336</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300308336</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>모모 네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lucasyonn@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>031-8016-5520</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lucasyonn</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>37117007</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37117007</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>에러퍼펙트 분당서현점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jungwonnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1436-5758</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>639</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2589</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1180875815</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1180875815</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bbolm@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hello_jininail</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>885</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>258</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1143</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>13399185</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13399185</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>seo0unnienail@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1429-9122</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>2434</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2341</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4775</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1335668367</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335668367</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>milkycoco95@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1365-1483</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xnCjDG</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>38</v>
+      </c>
+      <c r="R61" t="n">
+        <v>145</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1505688975</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1505688975</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>버니스네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>saebom96@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1381-7791</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>16</v>
+      </c>
+      <c r="R62" t="n">
+        <v>44</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1103701684</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1103701684</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>네일반짝</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>geochanggun@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1400-7948</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_shiny_b/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>111</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1963530909</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1963530909</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>뮤요네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rabong1219@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>306</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>18</v>
+      </c>
+      <c r="R64" t="n">
+        <v>324</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1549676698</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1549676698</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오로지푸스 앤 네일 스파</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>orosy2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1382-0859</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>116</v>
+      </c>
+      <c r="R65" t="n">
+        <v>241</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1948399629</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1948399629</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>리르네일 판교역점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2seul0601@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1308-4907</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rire__nail</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>5</v>
+      </c>
+      <c r="R66" t="n">
+        <v>180</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1213582322</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213582322</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>디에고푸스 판교점 네일어베인</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>twodragona@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1391-8131</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>80</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2075785121</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2075785121</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일신 판교점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>moijj@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>031-708-4142</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailshin_/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>39</v>
+      </c>
+      <c r="R68" t="n">
+        <v>273</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1768463815</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1768463815</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>디어뀨네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>roh_ys@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1389-5408</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dear.ccuu_nail</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>11</v>
+      </c>
+      <c r="R69" t="n">
+        <v>192</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2001491207</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001491207</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일아이</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sgocome@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1320-2619</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sgocome</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>550</v>
+      </c>
+      <c r="R70" t="n">
+        <v>616</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1852639386</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852639386</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일숲</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>olive322@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_soup_</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>27</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1564392316</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564392316</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>gywjd2303@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailinus</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>636</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>162</v>
+      </c>
+      <c r="R72" t="n">
+        <v>798</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1591004723</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1591004723</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>루미가넷 현대백화점 판교점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>tnwjdgnsi@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1443-1569</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://www.lumigarnet.com/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4</v>
+      </c>
+      <c r="R73" t="n">
+        <v>59</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>37197708</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37197708</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>비벨리</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>traveltrip11@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1371-1908</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>532</v>
+      </c>
+      <c r="R74" t="n">
+        <v>789</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1626230048</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1626230048</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>네일드와</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hellomj18@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1445-1545</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_de_wa</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>721</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>16</v>
+      </c>
+      <c r="R75" t="n">
+        <v>737</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1349678048</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349678048</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>손을그리다</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>tntpung@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>031-704-1009</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drawhand_nail/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>84</v>
+      </c>
+      <c r="R76" t="n">
+        <v>155</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>36398915</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36398915</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/판교_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/판교_네일샵.xlsx
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>예쁘다그대 네일</t>
+          <t>손을그리다</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ped7913@naver.com</t>
+          <t>tntpung@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>031-704-1009</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeudageudaenail</t>
+          <t>https://www.instagram.com/drawhand_nail/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="R2" t="n">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1048880915</t>
+          <t>36398915</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048880915</t>
+          <t>https://m.place.naver.com/place/36398915</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>예쁘다그대 네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>ped7913@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1466-0874</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>http://www.instagram.com/yebbeudageudaenail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1048880915</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1048880915</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>138</v>
+        <v>1159</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="R4" t="n">
-        <v>152</v>
+        <v>1254</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -838,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>쏘햅삐네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>ssohapbbi_nail@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1365-1459</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://www.instagram.com/ssohapbbi_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>1699230267</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/1699230267</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -932,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>쏘햅삐네일</t>
+          <t>루미가넷 현대백화점 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ssohapbbi_nail@naver.com</t>
+          <t>tnwjdgnsi@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1365-1459</t>
+          <t>0507-1443-1569</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssohapbbi_nail</t>
+          <t>http://www.lumigarnet.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>334</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>340</v>
+        <v>59</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1699230267</t>
+          <t>37197708</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699230267</t>
+          <t>https://m.place.naver.com/place/37197708</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더다인</t>
+          <t>네일신 판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>clarkjenny@naver.com</t>
+          <t>moijj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1448-2080</t>
+          <t>031-708-4142</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailshin_/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1079,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>234</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>273</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37870367</t>
+          <t>1768463815</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870367</t>
+          <t>https://m.place.naver.com/place/1768463815</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1317-6311</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1173,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>395</v>
+        <v>1035</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="R8" t="n">
-        <v>464</v>
+        <v>1156</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바비앤네일</t>
+          <t>그리너리프라이빗뷰티샵</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rladbrud8791@naver.com</t>
+          <t>q19900320@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1418-0917</t>
+          <t>0507-1446-1041</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 176</t>
+          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://barbienail.itpage.kr/</t>
+          <t>https://www.instagram.com/greenery_nail/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>306</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21733065</t>
+          <t>50639356</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21733065</t>
+          <t>https://m.place.naver.com/place/50639356</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>하르네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>cxd1000@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1305-3099</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1344,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1361,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1031</v>
+        <v>274</v>
       </c>
       <c r="Q10" t="n">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="R10" t="n">
-        <v>1152</v>
+        <v>310</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1402,39 +1406,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일탐</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kangjooho0519@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1344-3330</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1450,22 +1454,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1400616486</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400616486</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>팜네일유카리</t>
+          <t>수요일네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>micchudog@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1387-4579</t>
+          <t>0507-1333-9913</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
+          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palm_nail_yukari</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1549,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1434919594</t>
+          <t>1865078719</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434919594</t>
+          <t>https://m.place.naver.com/place/1865078719</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1594,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kshkjs1225@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1436-7943</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.suda</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>37851165</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37851165</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1684,34 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
+          <t>HENA BEAUTY LAB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lamour11@naver.com</t>
+          <t>amyloves_red@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1419-0757</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>http://pf.kakao.com/_zLygn</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1732,22 +1732,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>262</v>
+        <v>597</v>
       </c>
       <c r="Q14" t="n">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="R14" t="n">
-        <v>343</v>
+        <v>847</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>30844297</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/30844297</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HENA BEAUTY LAB</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>amyloves_red@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1419-0757</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zLygn</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>597</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="n">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="R15" t="n">
-        <v>847</v>
+        <v>184</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>30844297</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30844297</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
+          <t>로코코네일 판교본점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nailpalace@naver.com</t>
+          <t>nail_rococo@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>0507-1315-1583</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>https://linktr.ee/rococonail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="Q16" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>344</v>
+        <v>133</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>1008417568</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/1008417568</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1157</v>
+        <v>395</v>
       </c>
       <c r="Q17" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="R17" t="n">
-        <v>1252</v>
+        <v>464</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>숨숨네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>rnys11@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>0507-1334-7410</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://www.instagram.com/soomsoom.nail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1373</v>
+        <v>211</v>
       </c>
       <c r="Q18" t="n">
-        <v>567</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>1940</v>
+        <v>223</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1619651823</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1619651823</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일바니</t>
+          <t>바비앤네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>suna8457@naver.com</t>
+          <t>rladbrud8791@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1305-2049</t>
+          <t>0507-1418-0917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
+          <t>경기도 성남시 분당구 운중로 176</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail6unny</t>
+          <t>http://barbienail.itpage.kr/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1519571633</t>
+          <t>21733065</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519571633</t>
+          <t>https://m.place.naver.com/place/21733065</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2248,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일설렘</t>
+          <t>리르네일 판교역점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mistymoon5@naver.com</t>
+          <t>2seul0601@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1436-0914</t>
+          <t>0507-1308-4907</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailseolrem</t>
+          <t>https://www.instagram.com/rire__nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>361</v>
+        <v>175</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1622892642</t>
+          <t>1213582322</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1622892642</t>
+          <t>https://m.place.naver.com/place/1213582322</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>버베인네일 분당수내점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>llltwjhlll@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1375-0335</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>https://blog.naver.com/llltwjhlll</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>441</v>
+        <v>54</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="R21" t="n">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>2016496556</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/2016496556</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2436,29 +2436,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kshkjs1225@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1355-4142</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2468,7 +2464,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2489,17 +2485,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>1079</v>
       </c>
       <c r="Q22" t="n">
-        <v>66</v>
+        <v>524</v>
       </c>
       <c r="R22" t="n">
-        <v>78</v>
+        <v>1603</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1207469718</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207469718</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2530,30 +2526,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1466-0874</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R23" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>손끝에담다</t>
+          <t>후와네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cc850625@naver.com</t>
+          <t>kimnk980409@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1429-4102</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sondam41</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>447</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R24" t="n">
-        <v>16</v>
+        <v>465</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>199302625</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/199302625</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2714,44 +2714,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>오로지푸스 앤 네일 스파</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>orosy2020@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1382-0859</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1105</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="R25" t="n">
-        <v>1139</v>
+        <v>241</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>1948399629</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/1948399629</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2808,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>내일그리고네일</t>
+          <t>디에고푸스 판교점 네일어베인</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>major13564@naver.com</t>
+          <t>twodragona@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1397-7847</t>
+          <t>0507-1391-8131</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://instagram.com/tomorrow7836</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="Q26" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1389203098</t>
+          <t>2075785121</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389203098</t>
+          <t>https://m.place.naver.com/place/2075785121</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2902,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>woosy0225@naver.com</t>
+          <t>dlgksmf3595@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1491-7802</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/nailon7793</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2959,13 +2959,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>683</v>
+        <v>304</v>
       </c>
       <c r="Q27" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>741</v>
+        <v>316</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2974,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1655818723</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1655818723</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2996,39 +2996,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>꼼앤네일아트 속눈썹 서현역점</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ujin9132@naver.com</t>
+          <t>lds9525@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1403-8660</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 1동 2층 205호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ccom_heewon</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R28" t="n">
-        <v>154</v>
+        <v>359</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3068,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1495049038</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1495049038</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3090,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>퀸즈</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mam-hand@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1363-4230</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
-        <v>15</v>
+        <v>354</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1429117837</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429117837</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3184,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>퀸즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>candycara@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1491-7802</t>
+          <t>0507-1363-4230</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon7793</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1655818723</t>
+          <t>1429117837</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655818723</t>
+          <t>https://m.place.naver.com/place/1429117837</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3278,39 +3278,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>포쉬네일 AK분당점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lds9525@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>328</v>
+        <v>682</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="R31" t="n">
-        <v>359</v>
+        <v>740</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3372,29 +3372,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>네일아르떼</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>tpfla1999@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1375-0335</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3409,7 +3405,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3429,13 +3425,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>53</v>
+        <v>473</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="R32" t="n">
-        <v>84</v>
+        <v>510</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3462,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>디네일</t>
+          <t>메종드리엘</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>b_ye_bye@naver.com</t>
+          <t>lovelyzzzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1498-4179</t>
+          <t>0507-1363-0109</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
+          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://instagram.com/d.nail_4179</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3498,7 +3494,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3519,17 +3515,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="R33" t="n">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3534,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1139274960</t>
+          <t>1572212961</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139274960</t>
+          <t>https://m.place.naver.com/place/1572212961</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3560,29 +3556,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>예스네일</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lovmaria@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1320-2494</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ye_s_nail</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3597,7 +3593,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3617,13 +3613,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>660</v>
+        <v>555</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="R34" t="n">
-        <v>673</v>
+        <v>622</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3628,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1073307347</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073307347</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3654,34 +3650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3702,7 +3698,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3711,13 +3707,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>66</v>
+        <v>2434</v>
       </c>
       <c r="Q35" t="n">
-        <v>118</v>
+        <v>2342</v>
       </c>
       <c r="R35" t="n">
-        <v>184</v>
+        <v>4776</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,17 +3722,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3748,34 +3744,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>이마네일</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pdr0613@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1427-8952</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxlBPj</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3796,7 +3788,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3805,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R36" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1053041064</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053041064</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3842,29 +3834,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>로코코네일 판교본점</t>
+          <t>버니스네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nail_rococo@naver.com</t>
+          <t>saebom96@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1315-1583</t>
+          <t>0507-1381-7791</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
+          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://linktr.ee/rococonail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3874,7 +3866,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3890,22 +3882,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R37" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1008417568</t>
+          <t>1103701684</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008417568</t>
+          <t>https://m.place.naver.com/place/1103701684</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3936,34 +3928,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>후와네일</t>
+          <t>이마네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kimnk980409@naver.com</t>
+          <t>pdr0613@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>0507-1427-8952</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_yxlBPj</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3984,7 +3976,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3993,13 +3985,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>446</v>
+        <v>56</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R38" t="n">
-        <v>464</v>
+        <v>71</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1053041064</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1053041064</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4022,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>수요일네일</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>sgocome@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1333-9913</t>
+          <t>0507-1320-2619</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
+          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sgocome</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4062,12 +4054,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4087,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>550</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>617</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1865078719</t>
+          <t>1852639386</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865078719</t>
+          <t>https://m.place.naver.com/place/1852639386</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4124,29 +4116,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>그리너리프라이빗뷰티샵</t>
+          <t>더다인</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>q19900320@naver.com</t>
+          <t>clarkjenny@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1446-1041</t>
+          <t>0507-1448-2080</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/greenery_nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4156,7 +4148,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4177,17 +4169,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>237</v>
+        <v>6</v>
       </c>
       <c r="Q40" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>50639356</t>
+          <t>37870367</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/50639356</t>
+          <t>https://m.place.naver.com/place/37870367</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4218,39 +4210,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>메종드리엘</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>lovelyzzzzzzz@naver.com</t>
-        </is>
-      </c>
+          <t>MANYONENAIL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1363-0109</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
+          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_lzxfAn</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4266,22 +4250,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="Q41" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4274,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1572212961</t>
+          <t>1675486546</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572212961</t>
+          <t>https://m.place.naver.com/place/1675486546</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4312,29 +4296,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>예스네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>lovmaria@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1320-2494</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>http://www.instagram.com/ye_s_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4369,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>357</v>
+        <v>660</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="R42" t="n">
-        <v>386</v>
+        <v>673</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4368,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1073307347</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1073307347</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4406,25 +4390,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1436-7943</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://www.instagram.com/nail.suda</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4459,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1078</v>
+        <v>88</v>
       </c>
       <c r="Q43" t="n">
-        <v>524</v>
+        <v>100</v>
       </c>
       <c r="R43" t="n">
-        <v>1602</v>
+        <v>188</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,17 +4462,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>37851165</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/37851165</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4496,25 +4484,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>손끝에담다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>cc850625@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1429-4102</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://www.instagram.com/sondam41</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4529,7 +4521,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4540,7 +4532,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4549,13 +4541,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1297</v>
+        <v>12</v>
       </c>
       <c r="Q44" t="n">
-        <v>718</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>2015</v>
+        <v>16</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4556,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>199302625</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/199302625</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4578,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>달래네일</t>
+          <t>네일반짝</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>w130312@naver.com</t>
+          <t>geochanggun@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1471-1290</t>
+          <t>0507-1400-7948</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dalraenail</t>
+          <t>https://www.instagram.com/nail_shiny_b/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4643,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4650,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1453685923</t>
+          <t>1963530909</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453685923</t>
+          <t>https://m.place.naver.com/place/1963530909</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4672,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>하르네일</t>
+          <t>비벨리</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cxd1000@naver.com</t>
+          <t>traveltrip11@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4737,13 +4729,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>532</v>
       </c>
       <c r="R46" t="n">
-        <v>306</v>
+        <v>789</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4744,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4774,29 +4766,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4831,13 +4823,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>554</v>
+        <v>1952</v>
       </c>
       <c r="Q47" t="n">
-        <v>67</v>
+        <v>639</v>
       </c>
       <c r="R47" t="n">
-        <v>621</v>
+        <v>2591</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4838,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4868,25 +4860,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>네일바이라라</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>iam_jihye@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4921,13 +4917,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>166</v>
+        <v>360</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R48" t="n">
-        <v>189</v>
+        <v>389</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4932,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4958,29 +4954,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>라온네일클리닉 판교 본점</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1418-3314</t>
+          <t>0507-1389-6160</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sungunara226</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4995,7 +4991,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5015,13 +5011,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>67</v>
+        <v>316</v>
       </c>
       <c r="Q49" t="n">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="R49" t="n">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5026,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1137420501</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137420501</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5109,13 +5105,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q50" t="n">
         <v>13</v>
       </c>
       <c r="R50" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5134,7 +5130,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5142,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>숨숨네일</t>
+          <t>이브네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rnys11@naver.com</t>
+          <t>p4473@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1334-7410</t>
+          <t>0507-1405-0716</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soomsoom.nail</t>
+          <t>https://www.instagram.com/evenail_dj_hs</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5203,13 +5199,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>223</v>
+        <v>23</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5214,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1619651823</t>
+          <t>1345933789</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619651823</t>
+          <t>https://m.place.naver.com/place/1345933789</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5240,25 +5236,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>tpfla1999@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1355-4142</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="R52" t="n">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5308,17 +5308,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>1207469718</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/1207469718</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5330,29 +5330,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>팜네일유카리</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>micchudog@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>0507-1387-4579</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/palm_nail_yukari</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5383,17 +5383,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>201</v>
+        <v>4</v>
       </c>
       <c r="Q53" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>333</v>
+        <v>5</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5402,17 +5402,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1434919594</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1434919594</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5424,29 +5424,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>이브네일</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>am7734@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1405-0716</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evenail_dj_hs</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5481,13 +5477,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5496,17 +5492,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1345933789</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345933789</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5518,25 +5514,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>모아나네일</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7daystaste@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1359-2111</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/moana.jy</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>10</v>
+        <v>1105</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R55" t="n">
-        <v>12</v>
+        <v>1139</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5586,17 +5586,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1078179761</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078179761</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5608,29 +5608,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일오브윤 분당점</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>o___o373@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1366-7390</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o___o373</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5656,7 +5652,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5665,13 +5661,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1158</v>
+        <v>1299</v>
       </c>
       <c r="Q56" t="n">
-        <v>916</v>
+        <v>718</v>
       </c>
       <c r="R56" t="n">
-        <v>2074</v>
+        <v>2017</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5680,17 +5676,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1300308336</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5702,29 +5698,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>모모 네일</t>
+          <t>디네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lucasyonn@naver.com</t>
+          <t>b_ye_bye@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>031-8016-5520</t>
+          <t>0507-1498-4179</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
+          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lucasyonn</t>
+          <t>http://instagram.com/d.nail_4179</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5739,7 +5735,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5755,17 +5751,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5774,17 +5770,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>37117007</t>
+          <t>1139274960</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37117007</t>
+          <t>https://m.place.naver.com/place/1139274960</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5796,29 +5792,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>네일탐</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>kangjooho0519@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1344-3330</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5828,12 +5824,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5849,17 +5845,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1950</v>
+        <v>21</v>
       </c>
       <c r="Q58" t="n">
-        <v>639</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>2589</v>
+        <v>26</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5868,17 +5864,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1400616486</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1400616486</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5890,29 +5886,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>네일숲</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>olive322@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1429-8836</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>https://www.instagram.com/nail_soup_</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5947,13 +5939,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>885</v>
+        <v>27</v>
       </c>
       <c r="Q59" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1143</v>
+        <v>27</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5962,17 +5954,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>1564392316</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/1564392316</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5984,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>디어뀨네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>roh_ys@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1389-5408</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://www.instagram.com/dear.ccuu_nail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6041,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2434</v>
+        <v>183</v>
       </c>
       <c r="Q60" t="n">
-        <v>2341</v>
+        <v>11</v>
       </c>
       <c r="R60" t="n">
-        <v>4775</v>
+        <v>194</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6056,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>2001491207</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/2001491207</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6078,34 +6070,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6126,7 +6118,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6135,13 +6127,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>107</v>
+        <v>441</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="R61" t="n">
-        <v>145</v>
+        <v>511</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6150,17 +6142,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6172,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>버니스네일</t>
+          <t>네일팰리스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>saebom96@naver.com</t>
+          <t>nailpalace@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1381-7791</t>
+          <t>0507-1325-7941</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
+          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailpalace_official/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6204,7 +6196,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6225,17 +6217,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>28</v>
+        <v>243</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="R62" t="n">
-        <v>44</v>
+        <v>344</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6244,17 +6236,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1103701684</t>
+          <t>33928799</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103701684</t>
+          <t>https://m.place.naver.com/place/33928799</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6266,29 +6258,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일반짝</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>geochanggun@naver.com</t>
+          <t>silentforest_studio@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1400-7948</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_shiny_b/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6298,7 +6290,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6319,17 +6311,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="R63" t="n">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6338,17 +6330,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1963530909</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963530909</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6360,29 +6352,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
+          <t>달래네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rabong1219@naver.com</t>
+          <t>getitbt1534@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1471-1290</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/dalraenail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6417,13 +6409,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>324</v>
+        <v>211</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6432,17 +6424,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>1453685923</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/1453685923</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6454,39 +6446,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
+          <t>네일바니</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>orosy2020@naver.com</t>
+          <t>suna8457@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1305-2049</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://www.instagram.com/nail6unny</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6511,13 +6503,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Q65" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6526,17 +6518,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1519571633</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1519571633</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6548,29 +6540,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>리르네일 판교역점</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2seul0601@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1308-4907</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rire__nail</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6605,13 +6593,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="R66" t="n">
-        <v>180</v>
+        <v>257</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6620,17 +6608,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1213582322</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213582322</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6642,29 +6630,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>디에고푸스 판교점 네일어베인</t>
+          <t>네일설렘</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>twodragona@naver.com</t>
+          <t>mistymoon5@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1391-8131</t>
+          <t>0507-1436-0914</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
+          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailseolrem</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6674,7 +6662,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6695,17 +6683,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="R67" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6702,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2075785121</t>
+          <t>1622892642</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075785121</t>
+          <t>https://m.place.naver.com/place/1622892642</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6736,29 +6724,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일신 판교점</t>
+          <t>네일드와</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>moijj@naver.com</t>
+          <t>hellomj18@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>031-708-4142</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailshin_/</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6793,13 +6781,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>234</v>
+        <v>721</v>
       </c>
       <c r="Q68" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>273</v>
+        <v>737</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6796,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1768463815</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768463815</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6830,29 +6818,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>디어뀨네일</t>
+          <t>네일인어스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>roh_ys@naver.com</t>
+          <t>gywjd2303@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1389-5408</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dear.ccuu_nail</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6887,13 +6871,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>181</v>
+        <v>636</v>
       </c>
       <c r="Q69" t="n">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="R69" t="n">
-        <v>192</v>
+        <v>798</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,17 +6886,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2001491207</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001491207</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6924,29 +6908,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sgocome@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1320-2619</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgocome</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6977,17 +6961,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>66</v>
+        <v>1378</v>
       </c>
       <c r="Q70" t="n">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="R70" t="n">
-        <v>616</v>
+        <v>1945</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6996,17 +6980,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1852639386</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852639386</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7018,25 +7002,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일숲</t>
+          <t>라온네일클리닉 판교 본점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>olive322@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1418-3314</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_soup_</t>
+          <t>https://blog.naver.com/sungunara226</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7051,7 +7039,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7071,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="R71" t="n">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7086,17 +7074,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1564392316</t>
+          <t>1137420501</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564392316</t>
+          <t>https://m.place.naver.com/place/1137420501</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7096,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일인어스</t>
+          <t>모아나네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>gywjd2303@naver.com</t>
+          <t>7daystaste@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7121,12 +7109,12 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>http://instagram.com/moana.jy</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7161,13 +7149,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>636</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>798</v>
+        <v>12</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>1078179761</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/1078179761</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7198,29 +7186,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 판교점</t>
+          <t>모모 네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>tnwjdgnsi@naver.com</t>
+          <t>lucasyonn@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1443-1569</t>
+          <t>031-8016-5520</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
+          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.lumigarnet.com/</t>
+          <t>https://blog.naver.com/lucasyonn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7235,7 +7223,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7255,13 +7243,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37197708</t>
+          <t>37117007</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37197708</t>
+          <t>https://m.place.naver.com/place/37117007</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7292,29 +7280,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>안녕,예쁜손</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>bbolm@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1429-8836</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7349,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>257</v>
+        <v>885</v>
       </c>
       <c r="Q74" t="n">
-        <v>532</v>
+        <v>258</v>
       </c>
       <c r="R74" t="n">
-        <v>789</v>
+        <v>1143</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7364,17 +7352,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7386,29 +7374,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일드와</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hellomj18@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7443,13 +7431,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>721</v>
+        <v>264</v>
       </c>
       <c r="Q75" t="n">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="R75" t="n">
-        <v>737</v>
+        <v>345</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7458,17 +7446,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7480,29 +7468,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>손을그리다</t>
+          <t>내일그리고네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>major13564@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>031-704-1009</t>
+          <t>0507-1397-7847</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drawhand_nail/</t>
+          <t>https://instagram.com/tomorrow7836</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7537,13 +7525,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>71</v>
+        <v>517</v>
       </c>
       <c r="Q76" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="R76" t="n">
-        <v>155</v>
+        <v>564</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7552,17 +7540,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>36398915</t>
+          <t>1389203098</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36398915</t>
+          <t>https://m.place.naver.com/place/1389203098</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/판교_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/판교_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>손을그리다</t>
+          <t>후와네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>kimnk980409@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-704-1009</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drawhand_nail/</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>71</v>
+        <v>447</v>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>36398915</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36398915</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>예쁘다그대 네일</t>
+          <t>수요일네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ped7913@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1333-9913</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
+          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeudageudaenail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1048880915</t>
+          <t>1865078719</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048880915</t>
+          <t>https://m.place.naver.com/place/1865078719</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>포쉬네일 AK분당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1159</v>
+        <v>682</v>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="R4" t="n">
-        <v>1254</v>
+        <v>741</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>쏘햅삐네일</t>
+          <t>언제나네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ssohapbbi_nail@naver.com</t>
+          <t>cssyou@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1365-1459</t>
+          <t>0507-1433-3650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
+          <t>경기도 성남시 분당구 판교역로 240</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssohapbbi_nail</t>
+          <t>http://instagram.com/365.nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>342</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1699230267</t>
+          <t>38752862</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699230267</t>
+          <t>https://m.place.naver.com/place/38752862</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 판교점</t>
+          <t>숨숨네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tnwjdgnsi@naver.com</t>
+          <t>rnys11@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-1569</t>
+          <t>0507-1334-7410</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.lumigarnet.com/</t>
+          <t>https://www.instagram.com/soomsoom.nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37197708</t>
+          <t>1619651823</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37197708</t>
+          <t>https://m.place.naver.com/place/1619651823</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일신 판교점</t>
+          <t>손을그리다</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>moijj@naver.com</t>
+          <t>tntpung@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-708-4142</t>
+          <t>031-704-1009</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailshin_/</t>
+          <t>https://www.instagram.com/drawhand_nail/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1768463815</t>
+          <t>36398915</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768463815</t>
+          <t>https://m.place.naver.com/place/36398915</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>네일반짝</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>geochanggun@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1400-7948</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_shiny_b/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1160,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1177,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1035</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1156</v>
+        <v>111</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>1963530909</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/1963530909</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그리너리프라이빗뷰티샵</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q19900320@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1446-1041</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/greenery_nail/</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>237</v>
+        <v>2434</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>2342</v>
       </c>
       <c r="R9" t="n">
-        <v>306</v>
+        <v>4776</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>50639356</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/50639356</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하르네일</t>
+          <t>클라라</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cxd1000@naver.com</t>
+          <t>clala70@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>031-713-8444</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 2층 203호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/careerwoman7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>2059692384</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/2059692384</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>네일드와</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>hellomj18@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1454,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>721</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>145</v>
+        <v>737</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>수요일네일</t>
+          <t>루미가넷 현대백화점 판교점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>nuroonge@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1333-9913</t>
+          <t>0507-1443-1569</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.lumigarnet.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,7 +1536,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1865078719</t>
+          <t>37197708</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865078719</t>
+          <t>https://m.place.naver.com/place/37197708</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,30 +1598,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1466-0874</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="R13" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,34 +1692,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HENA BEAUTY LAB</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>amyloves_red@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1419-0757</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zLygn</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1732,22 +1736,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>597</v>
+        <v>1079</v>
       </c>
       <c r="Q14" t="n">
-        <v>250</v>
+        <v>524</v>
       </c>
       <c r="R14" t="n">
-        <v>847</v>
+        <v>1603</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1760,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>30844297</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30844297</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>HENA BEAUTY LAB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>amyloves_red@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1419-0757</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>http://pf.kakao.com/_zLygn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1831,17 +1835,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>66</v>
+        <v>597</v>
       </c>
       <c r="Q15" t="n">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="R15" t="n">
-        <v>184</v>
+        <v>847</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1854,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>30844297</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/30844297</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>로코코네일 판교본점</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nail_rococo@naver.com</t>
+          <t>dlgksmf3595@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1315-1583</t>
+          <t>0507-1491-7802</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
+          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://linktr.ee/rococonail</t>
+          <t>https://www.instagram.com/nailon7793</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1920,7 +1924,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>129</v>
+        <v>304</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>133</v>
+        <v>316</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1948,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1008417568</t>
+          <t>1655818723</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008417568</t>
+          <t>https://m.place.naver.com/place/1655818723</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1317-6311</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2003,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>395</v>
+        <v>1378</v>
       </c>
       <c r="Q17" t="n">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="R17" t="n">
-        <v>464</v>
+        <v>1945</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2060,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>숨숨네일</t>
+          <t>로코코네일 판교본점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rnys11@naver.com</t>
+          <t>nail_rococo@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1334-7410</t>
+          <t>0507-1315-1583</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soomsoom.nail</t>
+          <t>https://linktr.ee/rococonail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2108,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,12 +2136,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1619651823</t>
+          <t>1008417568</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619651823</t>
+          <t>https://m.place.naver.com/place/1008417568</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2154,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>바비앤네일</t>
+          <t>모모 네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rladbrud8791@naver.com</t>
+          <t>lucasyonn@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1418-0917</t>
+          <t>031-8016-5520</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 176</t>
+          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://barbienail.itpage.kr/</t>
+          <t>https://blog.naver.com/lucasyonn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2191,7 +2195,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2230,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>21733065</t>
+          <t>37117007</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21733065</t>
+          <t>https://m.place.naver.com/place/37117007</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2248,29 +2252,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>리르네일 판교역점</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2seul0601@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1308-4907</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rire__nail</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1213582322</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213582322</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>손끝에담다</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>cc850625@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1375-0335</t>
+          <t>0507-1429-4102</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>https://www.instagram.com/sondam41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>199302625</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/199302625</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2436,25 +2436,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>네일설렘</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>mistymoon5@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1436-0914</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://www.instagram.com/nailseolrem</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1079</v>
+        <v>361</v>
       </c>
       <c r="Q22" t="n">
-        <v>524</v>
+        <v>39</v>
       </c>
       <c r="R22" t="n">
-        <v>1603</v>
+        <v>400</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2508,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>1622892642</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/1622892642</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2526,34 +2530,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>네일숲</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>olive322@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1466-0874</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://www.instagram.com/nail_soup_</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1564392316</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1564392316</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2620,34 +2620,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>후와네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>kimnk980409@naver.com</t>
-        </is>
-      </c>
+          <t>MANYONENAIL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1342-1792</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_lzxfAn</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2668,7 +2660,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>465</v>
+        <v>109</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,12 +2684,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1675486546</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1675486546</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2714,39 +2706,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
+          <t>네일인어스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>orosy2020@naver.com</t>
+          <t>gywjd2303@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1382-0859</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2771,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>125</v>
+        <v>635</v>
       </c>
       <c r="Q25" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="R25" t="n">
-        <v>241</v>
+        <v>797</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,12 +2774,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2808,29 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>디에고푸스 판교점 네일어베인</t>
+          <t>네일신 판교점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>twodragona@naver.com</t>
+          <t>moijj@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1391-8131</t>
+          <t>031-708-4142</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailshin_/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2840,7 +2828,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2861,17 +2849,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="R26" t="n">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,12 +2868,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2075785121</t>
+          <t>1768463815</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075785121</t>
+          <t>https://m.place.naver.com/place/1768463815</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2902,29 +2890,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>네일팰리스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>nailpalace@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1491-7802</t>
+          <t>0507-1325-7941</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
+          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon7793</t>
+          <t>https://www.instagram.com/nailpalace_official/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2959,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="R27" t="n">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1655818723</t>
+          <t>33928799</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655818723</t>
+          <t>https://m.place.naver.com/place/33928799</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2996,39 +2984,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lds9525@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3053,13 +3041,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="R28" t="n">
-        <v>359</v>
+        <v>465</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,12 +3056,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3090,29 +3078,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>그리너리프라이빗뷰티샵</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>q19900320@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1446-1041</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://www.instagram.com/greenery_nail/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3147,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>321</v>
+        <v>237</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="R29" t="n">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,12 +3150,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>50639356</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/50639356</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3184,29 +3172,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>퀸즈</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>candycara@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1363-4230</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3216,12 +3204,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3237,17 +3225,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>1105</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="R30" t="n">
-        <v>15</v>
+        <v>1139</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,12 +3244,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1429117837</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429117837</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3278,29 +3266,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
+          <t>예스네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>woosy0225@naver.com</t>
+          <t>lovmaria@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1320-2494</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>http://www.instagram.com/ye_s_nail</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3335,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>682</v>
+        <v>660</v>
       </c>
       <c r="Q31" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>740</v>
+        <v>673</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,12 +3338,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1073307347</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1073307347</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3372,25 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
+          <t>바비앤네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tpfla1999@naver.com</t>
+          <t>rladbrud8791@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1418-0917</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 운중로 176</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>http://barbienail.itpage.kr/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3421,17 +3413,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="R32" t="n">
-        <v>510</v>
+        <v>9</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>21733065</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/21733065</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3462,29 +3454,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>메종드리엘</t>
+          <t>팜네일유카리</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lovelyzzzzzzz@naver.com</t>
+          <t>micchudog@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1363-0109</t>
+          <t>0507-1387-4579</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/palm_nail_yukari</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3494,7 +3486,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3515,17 +3507,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
         <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,12 +3526,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1572212961</t>
+          <t>1434919594</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572212961</t>
+          <t>https://m.place.naver.com/place/1434919594</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3556,34 +3548,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>이마네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>pdr0613@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1427-8952</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>http://pf.kakao.com/_yxlBPj</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3593,7 +3585,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3604,7 +3596,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>555</v>
+        <v>56</v>
       </c>
       <c r="Q34" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="R34" t="n">
-        <v>622</v>
+        <v>71</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,12 +3620,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>1053041064</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/1053041064</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3650,29 +3642,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>더다인</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>clarkjenny@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1448-2080</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,7 +3674,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3703,17 +3695,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2434</v>
+        <v>6</v>
       </c>
       <c r="Q35" t="n">
-        <v>2342</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>4776</v>
+        <v>7</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,12 +3714,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>37870367</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/37870367</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3744,35 +3736,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>yoj1116kr@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1369-6361</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3797,13 +3793,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>138</v>
+        <v>328</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="R36" t="n">
-        <v>152</v>
+        <v>359</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,12 +3808,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3834,29 +3830,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>버니스네일</t>
+          <t>디어뀨네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>saebom96@naver.com</t>
+          <t>roh_ys@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1381-7791</t>
+          <t>0507-1389-5408</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
+          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dear.ccuu_nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,7 +3862,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3887,17 +3883,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,12 +3902,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1103701684</t>
+          <t>2001491207</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103701684</t>
+          <t>https://m.place.naver.com/place/2001491207</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3928,29 +3924,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이마네일</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pdr0613@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1427-8952</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxlBPj</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3985,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="R38" t="n">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,12 +3996,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1053041064</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053041064</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4022,29 +4018,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sgocome@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1320-2619</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgocome</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4059,7 +4055,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4075,17 +4071,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="Q39" t="n">
-        <v>550</v>
+        <v>33</v>
       </c>
       <c r="R39" t="n">
-        <v>617</v>
+        <v>354</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,12 +4090,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1852639386</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852639386</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4116,29 +4112,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>더다인</t>
+          <t>내일그리고네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>clarkjenny@naver.com</t>
+          <t>major13564@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1448-2080</t>
+          <t>0507-1397-7847</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/tomorrow7836</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4148,7 +4144,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4169,17 +4165,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>6</v>
+        <v>517</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="R40" t="n">
-        <v>7</v>
+        <v>564</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,12 +4184,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>37870367</t>
+          <t>1389203098</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870367</t>
+          <t>https://m.place.naver.com/place/1389203098</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4210,26 +4206,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MANYONENAIL</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>라온네일클리닉 판교 본점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1418-3314</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lzxfAn</t>
+          <t>https://blog.naver.com/sungunara226</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4250,7 +4254,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4259,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="R41" t="n">
-        <v>109</v>
+        <v>350</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4278,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1675486546</t>
+          <t>1137420501</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675486546</t>
+          <t>https://m.place.naver.com/place/1137420501</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4296,29 +4300,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>예스네일</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lovmaria@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1320-2494</t>
+          <t>0507-1436-7943</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ye_s_nail</t>
+          <t>https://www.instagram.com/nail.suda</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4353,13 +4357,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>660</v>
+        <v>88</v>
       </c>
       <c r="Q42" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="R42" t="n">
-        <v>673</v>
+        <v>188</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,12 +4372,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1073307347</t>
+          <t>37851165</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073307347</t>
+          <t>https://m.place.naver.com/place/37851165</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4390,29 +4394,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kshkjs1225@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1436-7943</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.suda</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="R43" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37851165</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37851165</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4484,34 +4484,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>손끝에담다</t>
+          <t>휘우네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>cc850625@naver.com</t>
+          <t>jess778@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1429-4102</t>
+          <t>0507-1491-7588</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sondam41</t>
+          <t>http://pf.kakao.com/_eFEVn/chat</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4532,7 +4532,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>293</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R44" t="n">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>199302625</t>
+          <t>1758546666</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/199302625</t>
+          <t>https://m.place.naver.com/place/1758546666</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4578,34 +4578,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일반짝</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>geochanggun@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1400-7948</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_shiny_b/</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4626,7 +4626,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R45" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,12 +4650,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1963530909</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963530909</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4672,29 +4672,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>257</v>
+        <v>1952</v>
       </c>
       <c r="Q46" t="n">
-        <v>532</v>
+        <v>640</v>
       </c>
       <c r="R46" t="n">
-        <v>789</v>
+        <v>2592</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4766,29 +4766,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>모아나네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>7daystaste@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1436-5758</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>http://instagram.com/moana.jy</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4803,7 +4799,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4823,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1952</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="n">
-        <v>639</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>2591</v>
+        <v>12</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4838,12 +4834,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1078179761</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1078179761</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4860,29 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>네일바니</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>suna8457@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1305-2049</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://www.instagram.com/nail6unny</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4917,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>360</v>
+        <v>132</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4932,12 +4928,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1519571633</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1519571633</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4954,29 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>rabong1219@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4986,7 +4982,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5007,17 +5003,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>316</v>
+        <v>1036</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="R49" t="n">
-        <v>334</v>
+        <v>1157</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5026,12 +5022,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5048,39 +5044,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>휘우네일</t>
+          <t>메종드리엘</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jess778@naver.com</t>
+          <t>lovelyzzzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1491-7588</t>
+          <t>0507-1363-0109</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
+          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eFEVn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5096,22 +5092,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>293</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="R50" t="n">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5120,12 +5116,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1758546666</t>
+          <t>1572212961</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758546666</t>
+          <t>https://m.place.naver.com/place/1572212961</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5142,29 +5138,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>이브네일</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>p4473@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1405-0716</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evenail_dj_hs</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5179,7 +5175,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5199,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R51" t="n">
-        <v>23</v>
+        <v>623</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5214,12 +5210,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1345933789</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345933789</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5236,29 +5232,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kshkjs1225@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1355-4142</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5268,7 +5260,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5289,17 +5281,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="Q52" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="R52" t="n">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5308,12 +5300,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1207469718</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207469718</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5330,29 +5322,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>팜네일유카리</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>micchudog@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1387-4579</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palm_nail_yukari</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5387,13 +5375,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5402,12 +5390,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1434919594</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434919594</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5424,25 +5412,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>디에고푸스 판교점 네일어베인</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>twodragona@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1391-8131</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5452,7 +5444,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5473,17 +5465,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5492,12 +5484,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>2075785121</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/2075785121</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5514,29 +5506,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1355-4142</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5546,12 +5538,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5567,17 +5559,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1105</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="R55" t="n">
-        <v>1139</v>
+        <v>78</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5586,12 +5578,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>1207469718</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/1207469718</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5608,25 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>하르네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>cxd1000@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1305-3099</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5641,7 +5637,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5652,7 +5648,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5661,13 +5657,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1299</v>
+        <v>274</v>
       </c>
       <c r="Q56" t="n">
-        <v>718</v>
+        <v>36</v>
       </c>
       <c r="R56" t="n">
-        <v>2017</v>
+        <v>310</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,12 +5672,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5698,29 +5694,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>디네일</t>
+          <t>달래네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>b_ye_bye@naver.com</t>
+          <t>getitbt1534@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1498-4179</t>
+          <t>0507-1471-1290</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://instagram.com/d.nail_4179</t>
+          <t>https://www.instagram.com/dalraenail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5755,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5770,12 +5766,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1139274960</t>
+          <t>1453685923</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139274960</t>
+          <t>https://m.place.naver.com/place/1453685923</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5792,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일탐</t>
+          <t>비벨리</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kangjooho0519@naver.com</t>
+          <t>traveltrip11@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1344-3330</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5824,7 +5820,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5845,17 +5841,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>532</v>
       </c>
       <c r="R58" t="n">
-        <v>26</v>
+        <v>789</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5864,12 +5860,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1400616486</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400616486</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5886,25 +5882,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일숲</t>
+          <t>네일탐</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>olive322@naver.com</t>
+          <t>kangjooho0519@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1344-3330</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_soup_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1564392316</t>
+          <t>1400616486</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564392316</t>
+          <t>https://m.place.naver.com/place/1400616486</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5976,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>디어뀨네일</t>
+          <t>리르네일 판교역점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>roh_ys@naver.com</t>
+          <t>2seul0601@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1389-5408</t>
+          <t>0507-1308-4907</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dear.ccuu_nail</t>
+          <t>https://www.instagram.com/rire__nail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2001491207</t>
+          <t>1213582322</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001491207</t>
+          <t>https://m.place.naver.com/place/1213582322</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6070,29 +6070,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>디네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>b_ye_bye@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1498-4179</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>http://instagram.com/d.nail_4179</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>441</v>
+        <v>110</v>
       </c>
       <c r="Q61" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>511</v>
+        <v>111</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>1139274960</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/1139274960</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6164,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nailpalace@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6221,13 +6221,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>243</v>
+        <v>441</v>
       </c>
       <c r="Q62" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="R62" t="n">
-        <v>344</v>
+        <v>511</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6236,12 +6236,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6258,29 +6258,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>예쁘다그대 네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>ped7913@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>031-603-3011</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/yebbeudageudaenail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6290,7 +6286,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6311,17 +6307,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>333</v>
+        <v>13</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6330,12 +6326,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1048880915</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1048880915</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6352,29 +6348,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>달래네일</t>
+          <t>안녕,예쁜손</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>getitbt1534@naver.com</t>
+          <t>bbolm@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1471-1290</t>
+          <t>0507-1429-8836</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dalraenail</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6409,13 +6405,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>207</v>
+        <v>885</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>258</v>
       </c>
       <c r="R64" t="n">
-        <v>211</v>
+        <v>1143</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6424,12 +6420,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1453685923</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453685923</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6446,29 +6442,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일바니</t>
+          <t>퀸즈</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>suna8457@naver.com</t>
+          <t>candycara@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1305-2049</t>
+          <t>0507-1363-4230</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail6unny</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6478,7 +6474,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6499,17 +6495,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R65" t="n">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6518,12 +6514,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1519571633</t>
+          <t>1429117837</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519571633</t>
+          <t>https://m.place.naver.com/place/1429117837</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6540,25 +6536,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>laetitia5980@naver.com</t>
+          <t>sgocome@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1320-2619</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>https://blog.naver.com/sgocome</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6589,17 +6589,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="Q66" t="n">
-        <v>101</v>
+        <v>550</v>
       </c>
       <c r="R66" t="n">
-        <v>257</v>
+        <v>617</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,12 +6608,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>1852639386</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/1852639386</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6630,29 +6630,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일설렘</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mistymoon5@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1436-0914</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailseolrem</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>361</v>
+        <v>264</v>
       </c>
       <c r="Q67" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="R67" t="n">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1622892642</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1622892642</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6724,29 +6724,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일드와</t>
+          <t>버니스네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hellomj18@naver.com</t>
+          <t>saebom96@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1381-7791</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6777,17 +6777,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>721</v>
+        <v>29</v>
       </c>
       <c r="Q68" t="n">
         <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>737</v>
+        <v>45</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>1103701684</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/1103701684</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6818,25 +6818,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일인어스</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>gywjd2303@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6871,13 +6875,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>636</v>
+        <v>1159</v>
       </c>
       <c r="Q69" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="R69" t="n">
-        <v>798</v>
+        <v>1254</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,12 +6890,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6908,29 +6912,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>0507-1389-6160</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6945,7 +6949,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6965,13 +6969,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1378</v>
+        <v>316</v>
       </c>
       <c r="Q70" t="n">
-        <v>567</v>
+        <v>18</v>
       </c>
       <c r="R70" t="n">
-        <v>1945</v>
+        <v>334</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,12 +6984,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7002,29 +7006,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>라온네일클리닉 판교 본점</t>
+          <t>네일아르떼</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>tpfla1999@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1418-3314</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sungunara226</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>67</v>
+        <v>474</v>
       </c>
       <c r="Q71" t="n">
-        <v>283</v>
+        <v>37</v>
       </c>
       <c r="R71" t="n">
-        <v>350</v>
+        <v>511</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1137420501</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137420501</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7096,25 +7096,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>모아나네일</t>
+          <t>이브네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>7daystaste@naver.com</t>
+          <t>p4473@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1405-0716</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/moana.jy</t>
+          <t>https://www.instagram.com/evenail_dj_hs</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7149,13 +7153,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Q72" t="n">
         <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,12 +7168,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1078179761</t>
+          <t>1345933789</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078179761</t>
+          <t>https://m.place.naver.com/place/1345933789</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7186,29 +7190,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>모모 네일</t>
+          <t>네일바이라라</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lucasyonn@naver.com</t>
+          <t>iam_jihye@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>031-8016-5520</t>
+          <t>0507-1356-4115</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lucasyonn</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7223,7 +7227,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7239,17 +7243,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>5</v>
+        <v>360</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="R73" t="n">
-        <v>7</v>
+        <v>389</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,12 +7262,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37117007</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37117007</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7280,29 +7284,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>silentforest_studio@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1429-8836</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7312,7 +7316,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7333,17 +7337,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>885</v>
+        <v>201</v>
       </c>
       <c r="Q74" t="n">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="R74" t="n">
-        <v>1143</v>
+        <v>334</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7352,12 +7356,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7374,29 +7378,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
+          <t>쏘햅삐네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lamour11@naver.com</t>
+          <t>ssohapbbi_nail@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1365-1459</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>https://www.instagram.com/ssohapbbi_nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7431,13 +7435,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="Q75" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="R75" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7446,12 +7450,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>1699230267</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/1699230267</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7468,29 +7472,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>내일그리고네일</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>major13564@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1397-7847</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://instagram.com/tomorrow7836</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7516,7 +7516,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>517</v>
+        <v>1299</v>
       </c>
       <c r="Q76" t="n">
-        <v>47</v>
+        <v>719</v>
       </c>
       <c r="R76" t="n">
-        <v>564</v>
+        <v>2018</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1389203098</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389203098</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_nail/판교_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/판교_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>후와네일</t>
+          <t>숨숨네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kimnk980409@naver.com</t>
+          <t>rnys11@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>0507-1334-7410</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/soomsoom.nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>447</v>
+        <v>211</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>465</v>
+        <v>223</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1619651823</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1619651823</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,39 +658,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>수요일네일</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>loosetime@naver.com</t>
-        </is>
-      </c>
+          <t>HENA BEAUTY LAB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1333-9913</t>
+          <t>0507-1419-0757</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
+          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_zLygn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>597</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>847</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1865078719</t>
+          <t>30844297</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865078719</t>
+          <t>https://m.place.naver.com/place/30844297</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>woosy0225@naver.com</t>
-        </is>
-      </c>
+          <t>리르네일 판교역점</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1308-4907</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/rire__nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>682</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>741</v>
+        <v>180</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1213582322</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1213582322</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>언제나네일</t>
+          <t>네일바니</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cssyou@naver.com</t>
+          <t>suna8457@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1433-3650</t>
+          <t>0507-1305-2049</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 240</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/365.nail</t>
+          <t>https://www.instagram.com/nail6unny</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38752862</t>
+          <t>1519571633</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38752862</t>
+          <t>https://m.place.naver.com/place/1519571633</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>숨숨네일</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>rnys11@naver.com</t>
-        </is>
-      </c>
+          <t>팜네일유카리</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1334-7410</t>
+          <t>0507-1387-4579</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soomsoom.nail</t>
+          <t>https://www.instagram.com/palm_nail_yukari</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>211</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>223</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1000,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1619651823</t>
+          <t>1434919594</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619651823</t>
+          <t>https://m.place.naver.com/place/1434919594</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1022,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>손을그리다</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>031-704-1009</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drawhand_nail/</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>1079</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>524</v>
       </c>
       <c r="R7" t="n">
-        <v>155</v>
+        <v>1603</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36398915</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36398915</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1112,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일반짝</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>geochanggun@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1400-7948</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_shiny_b/</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1165,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R8" t="n">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1180,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1963530909</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963530909</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1202,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1436-7943</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://www.instagram.com/nail.suda</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1259,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2434</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2342</v>
+        <v>100</v>
       </c>
       <c r="R9" t="n">
-        <v>4776</v>
+        <v>188</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1274,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>37851165</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/37851165</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1296,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>클라라</t>
+          <t>언제나네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>clala70@naver.com</t>
+          <t>cssyou@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-713-8444</t>
+          <t>0507-1433-3650</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 2층 203호</t>
+          <t>경기도 성남시 분당구 판교역로 240</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/careerwoman7</t>
+          <t>http://instagram.com/365.nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2059692384</t>
+          <t>38752862</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059692384</t>
+          <t>https://m.place.naver.com/place/38752862</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1390,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일드와</t>
+          <t>수요일네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hellomj18@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1333-9913</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1463,17 +1443,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>721</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>737</v>
+        <v>3</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>1865078719</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/1865078719</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1484,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>루미가넷 현대백화점 판교점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>nuroonge@naver.com</t>
-        </is>
-      </c>
+          <t>네일설렘</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1443-1569</t>
+          <t>0507-1436-0914</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
+          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://www.lumigarnet.com/</t>
+          <t>https://www.instagram.com/nailseolrem</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,17 +1533,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>55</v>
+        <v>361</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="R12" t="n">
-        <v>59</v>
+        <v>400</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1552,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37197708</t>
+          <t>1622892642</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37197708</t>
+          <t>https://m.place.naver.com/place/1622892642</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1574,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>내일그리고네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>major13564@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1397-7847</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://instagram.com/tomorrow7836</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,13 +1631,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>107</v>
+        <v>517</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
-        <v>162</v>
+        <v>564</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1646,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1389203098</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1389203098</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1692,25 +1668,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>모모 네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>lucasyonn@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>031-8016-5520</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://blog.naver.com/lucasyonn</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1725,7 +1705,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,17 +1721,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1079</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>524</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1603</v>
+        <v>7</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>37117007</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/37117007</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1762,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HENA BEAUTY LAB</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>amyloves_red@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1419-0757</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zLygn</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1835,17 +1815,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>597</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="n">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="R15" t="n">
-        <v>847</v>
+        <v>184</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>30844297</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30844297</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1856,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>라온네일클리닉 판교 본점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1491-7802</t>
+          <t>0507-1418-3314</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon7793</t>
+          <t>https://blog.naver.com/sungunara226</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,7 +1893,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1933,13 +1913,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>304</v>
+        <v>67</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>283</v>
       </c>
       <c r="R16" t="n">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1655818723</t>
+          <t>1137420501</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655818723</t>
+          <t>https://m.place.naver.com/place/1137420501</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1950,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1378</v>
+        <v>1105</v>
       </c>
       <c r="Q17" t="n">
-        <v>567</v>
+        <v>34</v>
       </c>
       <c r="R17" t="n">
-        <v>1945</v>
+        <v>1139</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2064,39 +2044,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>로코코네일 판교본점</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nail_rococo@naver.com</t>
+          <t>yoj1116kr@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1315-1583</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://linktr.ee/rococonail</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2112,7 +2092,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>129</v>
+        <v>328</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="R18" t="n">
-        <v>133</v>
+        <v>359</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1008417568</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008417568</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2138,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>모모 네일</t>
+          <t>포쉬네일 AK분당점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lucasyonn@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>031-8016-5520</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lucasyonn</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,17 +2191,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>682</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>741</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>37117007</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37117007</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2232,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>모아나네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>7daystaste@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2265,12 +2245,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>http://instagram.com/moana.jy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>152</v>
+        <v>12</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1078179761</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1078179761</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2322,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>손끝에담다</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cc850625@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1429-4102</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sondam41</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2399,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="R21" t="n">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>199302625</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/199302625</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2436,29 +2416,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일설렘</t>
+          <t>바비앤네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mistymoon5@naver.com</t>
+          <t>kyo8967@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1436-0914</t>
+          <t>0507-1418-0917</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 2층 206호</t>
+          <t>경기도 성남시 분당구 운중로 176</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailseolrem</t>
+          <t>http://barbienail.itpage.kr/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,17 +2469,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>400</v>
+        <v>9</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1622892642</t>
+          <t>21733065</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1622892642</t>
+          <t>https://m.place.naver.com/place/21733065</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2530,25 +2510,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일숲</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>olive322@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1436-5758</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_soup_</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,7 +2547,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,13 +2567,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>27</v>
+        <v>1952</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="R23" t="n">
-        <v>27</v>
+        <v>2592</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1564392316</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564392316</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2620,26 +2604,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MANYONENAIL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>네일그자체</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wisp1205@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lzxfAn</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2660,7 +2648,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2669,13 +2657,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2672,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1675486546</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675486546</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2706,25 +2694,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일인어스</t>
+          <t>안녕,예쁜손</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>gywjd2303@naver.com</t>
+          <t>bbolm@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2759,13 +2751,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>635</v>
+        <v>887</v>
       </c>
       <c r="Q25" t="n">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="R25" t="n">
-        <v>797</v>
+        <v>1145</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2774,17 +2766,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2796,29 +2788,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일신 판교점</t>
+          <t>손끝에담다</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>moijj@naver.com</t>
+          <t>cc850625@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>031-708-4142</t>
+          <t>0507-1429-4102</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
+          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailshin_/</t>
+          <t>https://www.instagram.com/sondam41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2853,13 +2845,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2868,17 +2860,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1768463815</t>
+          <t>199302625</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768463815</t>
+          <t>https://m.place.naver.com/place/199302625</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2890,29 +2882,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nailpalace@naver.com</t>
+          <t>silentforest_studio@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2943,17 +2935,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="Q27" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="R27" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2954,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2984,29 +2976,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>네일바이라라</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>iam_jihye@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1317-6311</t>
+          <t>0507-1356-4115</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3041,13 +3033,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="R28" t="n">
-        <v>465</v>
+        <v>389</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3048,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3078,29 +3070,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>그리너리프라이빗뷰티샵</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>q19900320@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1446-1041</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/greenery_nail/</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,13 +3127,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>237</v>
+        <v>397</v>
       </c>
       <c r="Q29" t="n">
         <v>69</v>
       </c>
       <c r="R29" t="n">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3142,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>50639356</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/50639356</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3172,29 +3164,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>네일반짝</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>geochanggun@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1400-7948</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>https://www.instagram.com/nail_shiny_b/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3209,7 +3201,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3229,13 +3221,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1105</v>
+        <v>111</v>
       </c>
       <c r="Q30" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1139</v>
+        <v>111</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3236,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>1963530909</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/1963530909</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3258,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>예스네일</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lovmaria@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1320-2494</t>
+          <t>0507-1361-6532</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ye_s_nail</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3315,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>660</v>
+        <v>1159</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="R31" t="n">
-        <v>673</v>
+        <v>1254</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3330,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1073307347</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073307347</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3352,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>바비앤네일</t>
+          <t>퀸즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rladbrud8791@naver.com</t>
+          <t>candycara@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1418-0917</t>
+          <t>0507-1363-4230</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 176</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://barbienail.itpage.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3392,7 +3384,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3417,13 +3409,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3424,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>21733065</t>
+          <t>1429117837</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21733065</t>
+          <t>https://m.place.naver.com/place/1429117837</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3446,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>팜네일유카리</t>
+          <t>디어뀨네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>micchudog@naver.com</t>
+          <t>roh_ys@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1387-4579</t>
+          <t>0507-1389-5408</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
+          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palm_nail_yukari</t>
+          <t>https://www.instagram.com/dear.ccuu_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,13 +3503,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>184</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R33" t="n">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3518,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1434919594</t>
+          <t>2001491207</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434919594</t>
+          <t>https://m.place.naver.com/place/2001491207</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3548,34 +3540,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이마네일</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pdr0613@naver.com</t>
+          <t>sgocome@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1427-8952</t>
+          <t>0507-1320-2619</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
+          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxlBPj</t>
+          <t>https://blog.naver.com/sgocome</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3585,7 +3577,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3596,22 +3588,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>550</v>
       </c>
       <c r="R34" t="n">
-        <v>71</v>
+        <v>617</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3612,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1053041064</t>
+          <t>1852639386</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053041064</t>
+          <t>https://m.place.naver.com/place/1852639386</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3716,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3736,44 +3728,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yoj1116kr@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3793,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>328</v>
+        <v>556</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="R36" t="n">
-        <v>359</v>
+        <v>623</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3830,29 +3822,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>디어뀨네일</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>roh_ys@naver.com</t>
-        </is>
-      </c>
+          <t>예쁘다그대 네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1389-5408</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dear.ccuu_nail</t>
+          <t>http://www.instagram.com/yebbeudageudaenail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3887,13 +3871,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3886,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2001491207</t>
+          <t>1048880915</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001491207</t>
+          <t>https://m.place.naver.com/place/1048880915</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3924,29 +3908,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3961,7 +3945,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3972,7 +3956,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3981,13 +3965,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="Q38" t="n">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="R38" t="n">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +3980,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4018,34 +4002,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>휘우네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>jess778@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1491-7588</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>http://pf.kakao.com/_eFEVn/chat</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4066,7 +4050,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4075,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="R39" t="n">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>1758546666</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/1758546666</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4112,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>내일그리고네일</t>
+          <t>클라라</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>major13564@naver.com</t>
+          <t>clala70@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1397-7847</t>
+          <t>031-713-8444</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 2층 203호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://instagram.com/tomorrow7836</t>
+          <t>https://www.instagram.com/careerwoman7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4169,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1389203098</t>
+          <t>2059692384</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389203098</t>
+          <t>https://m.place.naver.com/place/2059692384</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4206,29 +4190,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>라온네일클리닉 판교 본점</t>
+          <t>하르네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>cxd1000@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1418-3314</t>
+          <t>0507-1305-3099</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sungunara226</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4243,7 +4227,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4263,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>67</v>
+        <v>276</v>
       </c>
       <c r="Q41" t="n">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,17 +4262,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1137420501</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137420501</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4300,29 +4284,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>kshkjs1225@naver.com</t>
-        </is>
-      </c>
+          <t>네일아르떼</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1436-7943</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.suda</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4357,13 +4333,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>88</v>
+        <v>474</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="R42" t="n">
-        <v>188</v>
+        <v>511</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4348,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>37851165</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37851165</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4394,25 +4370,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일그자체</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>wisp1205@naver.com</t>
-        </is>
-      </c>
+          <t>그리너리프라이빗뷰티샵</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1446-1041</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://www.instagram.com/greenery_nail/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4447,13 +4423,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="R43" t="n">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,17 +4438,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>50639356</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/50639356</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4484,34 +4460,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>휘우네일</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>jess778@naver.com</t>
-        </is>
-      </c>
+          <t>네일스튜디오미니</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1491-7588</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eFEVn/chat</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4532,7 +4504,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4541,13 +4513,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="R44" t="n">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4528,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1758546666</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758546666</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4578,34 +4550,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1365-1483</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4626,7 +4594,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4635,13 +4603,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="R45" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4618,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4672,29 +4640,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4709,7 +4677,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4729,13 +4697,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1952</v>
+        <v>441</v>
       </c>
       <c r="Q46" t="n">
-        <v>640</v>
+        <v>70</v>
       </c>
       <c r="R46" t="n">
-        <v>2592</v>
+        <v>511</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4712,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4766,25 +4734,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>모아나네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7daystaste@naver.com</t>
-        </is>
-      </c>
+          <t>뮤요네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://instagram.com/moana.jy</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4819,13 +4787,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10</v>
+        <v>316</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R47" t="n">
-        <v>12</v>
+        <v>334</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4802,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1078179761</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078179761</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4856,29 +4824,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일바니</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>suna8457@naver.com</t>
-        </is>
-      </c>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1305-2049</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail6unny</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4913,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>132</v>
+        <v>635</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="R48" t="n">
-        <v>136</v>
+        <v>798</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4888,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1519571633</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519571633</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4950,24 +4910,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코코네일</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>jjuahlee@naver.com</t>
-        </is>
-      </c>
+          <t>손 꽃처럼예쁘다</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1355-4142</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5007,13 +4963,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1036</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="n">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="R49" t="n">
-        <v>1157</v>
+        <v>78</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,17 +4978,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>1207469718</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/1207469718</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5000,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>메종드리엘</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lovelyzzzzzzz@naver.com</t>
+          <t>dlgksmf3595@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1363-0109</t>
+          <t>0507-1491-7802</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
+          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailon7793</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5076,7 +5032,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5097,17 +5053,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>305</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="R50" t="n">
-        <v>43</v>
+        <v>317</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,17 +5072,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1572212961</t>
+          <t>1655818723</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572212961</t>
+          <t>https://m.place.naver.com/place/1655818723</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5138,29 +5094,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5195,13 +5151,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>556</v>
+        <v>1378</v>
       </c>
       <c r="Q51" t="n">
-        <v>67</v>
+        <v>568</v>
       </c>
       <c r="R51" t="n">
-        <v>623</v>
+        <v>1946</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5166,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5232,25 +5188,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>laetitia5980@naver.com</t>
-        </is>
-      </c>
+          <t>예스네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1320-2494</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>http://www.instagram.com/ye_s_nail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5285,13 +5241,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>156</v>
+        <v>660</v>
       </c>
       <c r="Q52" t="n">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="R52" t="n">
-        <v>257</v>
+        <v>673</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5300,17 +5256,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>1073307347</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/1073307347</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5322,25 +5278,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>디네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>b_ye_bye@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1498-4179</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>http://instagram.com/d.nail_4179</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5375,13 +5335,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,17 +5350,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>1139274960</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/1139274960</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5412,39 +5372,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>디에고푸스 판교점 네일어베인</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>twodragona@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1391-8131</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5460,22 +5420,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R54" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5444,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2075785121</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075785121</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5506,29 +5466,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kshkjs1225@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1355-4142</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5538,7 +5498,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5559,17 +5519,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>2434</v>
       </c>
       <c r="Q55" t="n">
-        <v>66</v>
+        <v>2342</v>
       </c>
       <c r="R55" t="n">
-        <v>78</v>
+        <v>4776</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5538,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1207469718</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207469718</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5600,29 +5560,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>하르네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>cxd1000@naver.com</t>
-        </is>
-      </c>
+          <t>이브네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1405-0716</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/evenail_dj_hs</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5657,13 +5613,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>310</v>
+        <v>23</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5628,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>1345933789</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/1345933789</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5694,29 +5650,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>달래네일</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>getitbt1534@naver.com</t>
-        </is>
-      </c>
+          <t>네일드와</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1471-1290</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dalraenail</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5751,13 +5703,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>208</v>
+        <v>721</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R57" t="n">
-        <v>212</v>
+        <v>737</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5718,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1453685923</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453685923</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5788,29 +5740,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>쏘햅삐네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>ssohapbbi_nail@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1365-1459</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>https://www.instagram.com/ssohapbbi_nail</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5845,13 +5797,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="Q58" t="n">
-        <v>532</v>
+        <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>789</v>
+        <v>342</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5812,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1699230267</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1699230267</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5882,39 +5834,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일탐</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>kangjooho0519@naver.com</t>
-        </is>
-      </c>
+          <t>MANYONENAIL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1344-3330</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
+          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_lzxfAn</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5930,22 +5874,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5898,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1400616486</t>
+          <t>1675486546</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400616486</t>
+          <t>https://m.place.naver.com/place/1675486546</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5976,29 +5920,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>리르네일 판교역점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2seul0601@naver.com</t>
-        </is>
-      </c>
+          <t>비벨리</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1308-4907</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rire__nail</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6033,13 +5973,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>532</v>
       </c>
       <c r="R60" t="n">
-        <v>180</v>
+        <v>789</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +5988,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1213582322</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213582322</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6070,29 +6010,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>디네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>b_ye_bye@naver.com</t>
-        </is>
-      </c>
+          <t>네일숲</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1498-4179</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/d.nail_4179</t>
+          <t>https://www.instagram.com/nail_soup_</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6127,13 +6059,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6142,17 +6074,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1139274960</t>
+          <t>1564392316</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139274960</t>
+          <t>https://m.place.naver.com/place/1564392316</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6164,29 +6096,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>네일탐</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>kangjooho0519@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1344-3330</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6196,7 +6128,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6217,17 +6149,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="Q62" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="R62" t="n">
-        <v>511</v>
+        <v>26</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6236,17 +6168,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>1400616486</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/1400616486</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6258,30 +6190,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>예쁘다그대 네일</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ped7913@naver.com</t>
-        </is>
-      </c>
+          <t>이마네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1427-8952</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeudageudaenail</t>
+          <t>http://pf.kakao.com/_yxlBPj</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6302,7 +6234,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6311,13 +6243,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R63" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6258,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1048880915</t>
+          <t>1053041064</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048880915</t>
+          <t>https://m.place.naver.com/place/1053041064</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6348,29 +6280,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1429-8836</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,7 +6313,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6396,7 +6324,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6405,13 +6333,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>885</v>
+        <v>1299</v>
       </c>
       <c r="Q64" t="n">
-        <v>258</v>
+        <v>719</v>
       </c>
       <c r="R64" t="n">
-        <v>1143</v>
+        <v>2018</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6348,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6442,24 +6370,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>퀸즈</t>
+          <t>버니스네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>candycara@naver.com</t>
+          <t>saebom96@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1363-4230</t>
+          <t>0507-1381-7791</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
+          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6499,13 +6427,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R65" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,17 +6442,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1429117837</t>
+          <t>1103701684</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429117837</t>
+          <t>https://m.place.naver.com/place/1103701684</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6536,29 +6464,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>네일신 판교점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sgocome@naver.com</t>
+          <t>moijj@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1320-2619</t>
+          <t>031-708-4142</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgocome</t>
+          <t>https://www.instagram.com/nailshin_/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6573,7 +6501,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6589,17 +6517,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="Q66" t="n">
-        <v>550</v>
+        <v>39</v>
       </c>
       <c r="R66" t="n">
-        <v>617</v>
+        <v>273</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,17 +6536,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1852639386</t>
+          <t>1768463815</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852639386</t>
+          <t>https://m.place.naver.com/place/1768463815</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6630,29 +6558,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>lamour11@naver.com</t>
-        </is>
-      </c>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6662,7 +6586,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6683,17 +6607,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>264</v>
+        <v>1037</v>
       </c>
       <c r="Q67" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="R67" t="n">
-        <v>345</v>
+        <v>1158</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,17 +6626,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6724,29 +6648,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>버니스네일</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>saebom96@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1381-7791</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6756,7 +6676,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6777,17 +6697,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="Q68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,17 +6716,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1103701684</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103701684</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6818,29 +6738,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>루미가넷 현대백화점 판교점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>nuroonge@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1443-1569</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 판교점 4층 루미가넷</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>http://www.lumigarnet.com/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6871,17 +6791,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1159</v>
+        <v>55</v>
       </c>
       <c r="Q69" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>1254</v>
+        <v>59</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,17 +6810,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>37197708</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/37197708</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6912,29 +6832,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
+          <t>로코코네일 판교본점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>rabong1219@naver.com</t>
+          <t>nail_rococo@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1315-1583</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>https://linktr.ee/rococonail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6960,7 +6880,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6969,13 +6889,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>316</v>
+        <v>129</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,17 +6904,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>1008417568</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/1008417568</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7006,25 +6926,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>tpfla1999@naver.com</t>
-        </is>
-      </c>
+          <t>달래네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1471-1290</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>https://www.instagram.com/dalraenail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7059,13 +6979,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>474</v>
+        <v>208</v>
       </c>
       <c r="Q71" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>511</v>
+        <v>212</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,17 +6994,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>1453685923</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/1453685923</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7096,29 +7016,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>이브네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>p4473@naver.com</t>
-        </is>
-      </c>
+          <t>디에고푸스 판교점 네일어베인</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1405-0716</t>
+          <t>0507-1391-8131</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evenail_dj_hs</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7128,7 +7044,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7149,17 +7065,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7084,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1345933789</t>
+          <t>2075785121</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345933789</t>
+          <t>https://m.place.naver.com/place/2075785121</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7190,29 +7106,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>후와네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>kimnk980409@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7247,13 +7163,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>360</v>
+        <v>447</v>
       </c>
       <c r="Q73" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="R73" t="n">
-        <v>389</v>
+        <v>465</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7262,17 +7178,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7284,29 +7200,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>네일팰리스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>nailpalace@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>0507-1325-7941</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailpalace_official/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7316,7 +7232,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7337,17 +7253,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="Q74" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="R74" t="n">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7356,17 +7272,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>33928799</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/33928799</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7378,29 +7294,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>쏘햅삐네일</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ssohapbbi_nail@naver.com</t>
-        </is>
-      </c>
+          <t>메종드리엘</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1365-1459</t>
+          <t>0507-1363-0109</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
+          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssohapbbi_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7410,7 +7322,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7431,17 +7343,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>336</v>
+        <v>4</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="R75" t="n">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,17 +7362,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1699230267</t>
+          <t>1572212961</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699230267</t>
+          <t>https://m.place.naver.com/place/1572212961</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7472,25 +7384,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>손을그리다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>tntpung@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>031-704-1009</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://www.instagram.com/drawhand_nail/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7505,7 +7421,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7516,7 +7432,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7525,13 +7441,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1299</v>
+        <v>71</v>
       </c>
       <c r="Q76" t="n">
-        <v>719</v>
+        <v>84</v>
       </c>
       <c r="R76" t="n">
-        <v>2018</v>
+        <v>155</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7540,17 +7456,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>36398915</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/36398915</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/판교_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/판교_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>숨숨네일</t>
+          <t>네일탐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rnys11@naver.com</t>
+          <t>kangjooho0519@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-7410</t>
+          <t>0507-1344-3330</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soomsoom.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>223</v>
+        <v>26</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1619651823</t>
+          <t>1400616486</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619651823</t>
+          <t>https://m.place.naver.com/place/1400616486</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HENA BEAUTY LAB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>milkycoco95@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1419-0757</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zLygn</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>597</v>
+        <v>107</v>
       </c>
       <c r="Q3" t="n">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="R3" t="n">
-        <v>847</v>
+        <v>145</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>30844297</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30844297</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,25 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리르네일 판교역점</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>더블트리</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>doubletree-lash@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1308-4907</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rire__nail</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1213582322</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213582322</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -838,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일바니</t>
+          <t>팜네일유카리</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>suna8457@naver.com</t>
+          <t>micchudog@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1305-2049</t>
+          <t>0507-1387-4579</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail6unny</t>
+          <t>https://www.instagram.com/palm_nail_yukari</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>136</v>
+        <v>5</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1519571633</t>
+          <t>1434919594</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519571633</t>
+          <t>https://m.place.naver.com/place/1434919594</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -932,25 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>팜네일유카리</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>손끝에담다</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cc850625@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1387-4579</t>
+          <t>0507-1429-4102</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 상가 1층 1014호</t>
+          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palm_nail_yukari</t>
+          <t>https://www.instagram.com/sondam41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1434919594</t>
+          <t>199302625</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434919594</t>
+          <t>https://m.place.naver.com/place/199302625</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1022,25 +1030,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>uijn_dd@naver.com</t>
-        </is>
-      </c>
+          <t>포쉬네일 AK분당점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1416-2324</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1079</v>
+        <v>681</v>
       </c>
       <c r="Q7" t="n">
-        <v>524</v>
+        <v>58</v>
       </c>
       <c r="R7" t="n">
-        <v>1603</v>
+        <v>739</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1112,25 +1120,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>laetitia5980@naver.com</t>
-        </is>
-      </c>
+          <t>퀸즈</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1363-4230</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1140,7 +1148,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1161,17 +1169,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>257</v>
+        <v>17</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1180,17 +1188,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>1429117837</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/1429117837</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1205,15 +1213,11 @@
           <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>kshkjs1225@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1436-7943</t>
+          <t>0507-1355-4142</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1224,7 +1228,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.suda</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1255,17 +1259,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="R9" t="n">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1274,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37851165</t>
+          <t>1207469718</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37851165</t>
+          <t>https://m.place.naver.com/place/1207469718</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1296,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>언제나네일</t>
+          <t>메종드리엘</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cssyou@naver.com</t>
+          <t>lovelyzzzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1433-3650</t>
+          <t>0507-1363-0109</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 240</t>
+          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://instagram.com/365.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1328,7 +1332,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1349,17 +1353,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38752862</t>
+          <t>1572212961</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38752862</t>
+          <t>https://m.place.naver.com/place/1572212961</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1394,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>수요일네일</t>
+          <t>네일숲</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>olive322@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1333-9913</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_soup_</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1865078719</t>
+          <t>1564392316</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865078719</t>
+          <t>https://m.place.naver.com/place/1564392316</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,11 @@
           <t>네일설렘</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mistymoon5@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1574,29 +1578,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>내일그리고네일</t>
+          <t>달래네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>major13564@naver.com</t>
+          <t>gyerimong2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1397-7847</t>
+          <t>0507-1471-1290</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://instagram.com/tomorrow7836</t>
+          <t>https://www.instagram.com/dalraenail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1631,13 +1635,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>517</v>
+        <v>208</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>564</v>
+        <v>212</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1646,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1389203098</t>
+          <t>1453685923</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389203098</t>
+          <t>https://m.place.naver.com/place/1453685923</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1668,29 +1672,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>모모 네일</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lucasyonn@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>031-8016-5520</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lucasyonn</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,22 +1716,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>1300</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>720</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>2020</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1740,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37117007</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37117007</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1762,29 +1762,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>휘우네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>tjsdud7851@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1491-7588</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>http://pf.kakao.com/_eFEVn/chat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>66</v>
+        <v>294</v>
       </c>
       <c r="Q15" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>184</v>
+        <v>307</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1834,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>1758546666</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/1758546666</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1856,29 +1856,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>라온네일클리닉 판교 본점</t>
+          <t>숨숨네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>whateverido_o@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1418-3314</t>
+          <t>0507-1334-7410</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sungunara226</t>
+          <t>https://www.instagram.com/soomsoom.nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="Q16" t="n">
-        <v>283</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>350</v>
+        <v>223</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1137420501</t>
+          <t>1619651823</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137420501</t>
+          <t>https://m.place.naver.com/place/1619651823</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1950,29 +1950,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>더다인</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>clarkjenny@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1448-2080</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1105</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1139</v>
+        <v>7</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>37870367</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/37870367</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2044,39 +2044,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일 조안</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>yoj1116kr@naver.com</t>
-        </is>
-      </c>
+          <t>네일바니</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1305-2049</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하 2층 레드존 2106호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/nail6unny</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2101,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>328</v>
+        <v>132</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>359</v>
+        <v>136</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1519571633</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1519571633</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2138,29 +2134,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>woosy0225@naver.com</t>
-        </is>
-      </c>
+          <t>클라라</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>031-713-8444</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 2층 203호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/careerwoman7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,13 +2187,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>682</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,17 +2202,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>2059692384</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/2059692384</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2232,30 +2224,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>모아나네일</t>
+          <t>이마네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7daystaste@naver.com</t>
+          <t>pdr0613@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1427-8952</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/moana.jy</t>
+          <t>http://pf.kakao.com/_yxlBPj</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2276,7 +2272,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2285,13 +2281,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,17 +2296,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1078179761</t>
+          <t>1053041064</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078179761</t>
+          <t>https://m.place.naver.com/place/1053041064</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2322,29 +2318,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lamour11@naver.com</t>
+          <t>sgocome@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1320-2619</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>https://blog.naver.com/sgocome</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2359,7 +2355,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2375,17 +2371,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="Q21" t="n">
-        <v>81</v>
+        <v>550</v>
       </c>
       <c r="R21" t="n">
-        <v>345</v>
+        <v>617</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2394,17 +2390,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>1852639386</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/1852639386</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2416,29 +2412,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>바비앤네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kyo8967@naver.com</t>
-        </is>
-      </c>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1418-0917</t>
+          <t>0507-1305-3099</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 176</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://barbienail.itpage.kr/</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2469,17 +2461,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="R22" t="n">
-        <v>9</v>
+        <v>313</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2488,17 +2480,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>21733065</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21733065</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2510,29 +2502,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2547,7 +2539,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2567,13 +2559,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1952</v>
+        <v>264</v>
       </c>
       <c r="Q23" t="n">
-        <v>640</v>
+        <v>81</v>
       </c>
       <c r="R23" t="n">
-        <v>2592</v>
+        <v>345</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2574,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2596,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2617,12 +2609,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2657,13 +2649,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>169</v>
+        <v>1079</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>524</v>
       </c>
       <c r="R24" t="n">
-        <v>192</v>
+        <v>1603</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2672,17 +2664,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2694,29 +2686,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>버니스네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>saebom96@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1429-8836</t>
+          <t>0507-1381-7791</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2726,7 +2718,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2747,17 +2739,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>887</v>
+        <v>29</v>
       </c>
       <c r="Q25" t="n">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>1145</v>
+        <v>45</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2766,17 +2758,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>1103701684</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/1103701684</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2788,34 +2780,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>손끝에담다</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>cc850625@naver.com</t>
-        </is>
-      </c>
+          <t>MANYONENAIL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1429-4102</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 156 상가동 1층 109호</t>
+          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sondam41</t>
+          <t>http://pf.kakao.com/_lzxfAn</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2836,7 +2820,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2845,13 +2829,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2860,17 +2844,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>199302625</t>
+          <t>1675486546</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/199302625</t>
+          <t>https://m.place.naver.com/place/1675486546</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2882,34 +2866,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>yoj1116kr@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2935,17 +2919,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>201</v>
+        <v>328</v>
       </c>
       <c r="Q27" t="n">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2976,34 +2960,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3013,7 +2997,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3033,13 +3017,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="R28" t="n">
-        <v>389</v>
+        <v>163</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3048,17 +3032,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3070,29 +3054,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1317-6311</t>
+          <t>0507-1361-6532</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3127,13 +3111,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>397</v>
+        <v>1159</v>
       </c>
       <c r="Q29" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="R29" t="n">
-        <v>466</v>
+        <v>1254</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3142,17 +3126,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3164,29 +3148,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일반짝</t>
+          <t>모아나네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>geochanggun@naver.com</t>
+          <t>moana48@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1400-7948</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오 월드마크 1층 64호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_shiny_b/</t>
+          <t>http://instagram.com/moana.jy</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3221,13 +3201,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3236,17 +3216,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1963530909</t>
+          <t>1078179761</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963530909</t>
+          <t>https://m.place.naver.com/place/1078179761</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3258,29 +3238,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1361-6532</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3315,13 +3291,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1159</v>
+        <v>156</v>
       </c>
       <c r="Q31" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R31" t="n">
-        <v>1254</v>
+        <v>257</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3330,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3352,29 +3328,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>퀸즈</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>candycara@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1363-4230</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-5 1층101호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3384,12 +3360,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3405,17 +3381,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>1105</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="R32" t="n">
-        <v>17</v>
+        <v>1139</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3424,17 +3400,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1429117837</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429117837</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3446,29 +3422,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>디어뀨네일</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roh_ys@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1389-5408</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dear.ccuu_nail</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3503,13 +3479,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="R33" t="n">
-        <v>194</v>
+        <v>468</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3518,17 +3494,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2001491207</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001491207</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3540,29 +3516,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>예쁘다그대 네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sgocome@naver.com</t>
+          <t>ped7913@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1320-2619</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 432 제일프라자 2층 네일아이</t>
+          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgocome</t>
+          <t>http://www.instagram.com/yebbeudageudaenail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3577,7 +3549,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3593,17 +3565,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="n">
-        <v>550</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>617</v>
+        <v>13</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3612,17 +3584,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1852639386</t>
+          <t>1048880915</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852639386</t>
+          <t>https://m.place.naver.com/place/1048880915</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3634,29 +3606,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>더다인</t>
+          <t>리르네일 판교역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>clarkjenny@naver.com</t>
+          <t>2seul0601@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1448-2080</t>
+          <t>0507-1308-4907</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 209호 어바웃뷰티</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하1층 레드존 B1053호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rire__nail</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3666,7 +3638,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3687,17 +3659,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3706,17 +3678,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>37870367</t>
+          <t>1213582322</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870367</t>
+          <t>https://m.place.naver.com/place/1213582322</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3728,29 +3700,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>안녕,예쁜손</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>bbolm@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1429-8836</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3765,7 +3737,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3785,13 +3757,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>556</v>
+        <v>888</v>
       </c>
       <c r="Q36" t="n">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="R36" t="n">
-        <v>623</v>
+        <v>1146</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3800,17 +3772,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3822,21 +3794,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>예쁘다그대 네일</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>iam_jihye@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 34 1층 103호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeudageudaenail</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3871,13 +3851,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>360</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="R37" t="n">
-        <v>13</v>
+        <v>389</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3886,17 +3866,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1048880915</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048880915</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3908,34 +3888,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>leehhnail@naver.com</t>
-        </is>
-      </c>
+          <t>비벨리</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3945,7 +3921,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3965,13 +3941,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>532</v>
       </c>
       <c r="R38" t="n">
-        <v>162</v>
+        <v>789</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3980,17 +3956,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4002,39 +3978,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>휘우네일</t>
+          <t>수요일네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jess778@naver.com</t>
+          <t>vision143@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1491-7588</t>
+          <t>0507-1333-9913</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B122-1호 휘우네일</t>
+          <t>경기도 성남시 분당구 판교로 375 에메트타운 1층 수요일네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eFEVn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4050,22 +4026,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>306</v>
+        <v>3</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4074,17 +4050,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1758546666</t>
+          <t>1865078719</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758546666</t>
+          <t>https://m.place.naver.com/place/1865078719</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4096,29 +4072,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>클라라</t>
+          <t>네일팰리스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>clala70@naver.com</t>
+          <t>nailpalace@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>031-713-8444</t>
+          <t>0507-1325-7941</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 2층 203호</t>
+          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/careerwoman7</t>
+          <t>https://www.instagram.com/nailpalace_official/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4153,13 +4129,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4144,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2059692384</t>
+          <t>33928799</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059692384</t>
+          <t>https://m.place.naver.com/place/33928799</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4190,29 +4166,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>하르네일</t>
+          <t>디어뀨네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cxd1000@naver.com</t>
+          <t>roh_ys@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1389-5408</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 판교로 433 2층 7호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/dear.ccuu_nail</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,13 +4223,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4238,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>2001491207</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/2001491207</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4284,21 +4260,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>스타네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ejkim0422@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 판교로 430 건영상가 1층 111호 스타네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4308,7 +4288,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4329,17 +4309,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>474</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>511</v>
+        <v>13</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4348,17 +4328,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>959506934</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/959506934</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4370,25 +4350,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>그리너리프라이빗뷰티샵</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>모모 네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lucasyonn@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1446-1041</t>
+          <t>031-8016-5520</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
+          <t>경기도 성남시 분당구 판교로25번길 22-6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/greenery_nail/</t>
+          <t>https://blog.naver.com/lucasyonn</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4403,7 +4387,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4419,17 +4403,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>237</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4438,17 +4422,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>50639356</t>
+          <t>37117007</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/50639356</t>
+          <t>https://m.place.naver.com/place/37117007</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4460,25 +4444,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>이브네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>p4473@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1405-0716</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://www.instagram.com/evenail_dj_hs</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4513,13 +4501,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4528,17 +4516,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>1345933789</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/1345933789</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4550,25 +4538,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4603,13 +4595,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>138</v>
+        <v>317</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R45" t="n">
-        <v>152</v>
+        <v>335</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4618,17 +4610,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4640,29 +4632,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>내일그리고네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>major13564@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1397-7847</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>https://instagram.com/tomorrow7836</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4697,13 +4689,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="Q46" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="R46" t="n">
-        <v>511</v>
+        <v>564</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4712,17 +4704,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>1389203098</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/1389203098</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4734,25 +4726,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>디에고푸스 판교점 네일어베인</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>twodragona@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1391-8131</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4762,7 +4758,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4783,17 +4779,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4802,17 +4798,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>2075785121</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/2075785121</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4824,21 +4820,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일인어스</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>언제나네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>cssyou@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1433-3650</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로 240</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>http://instagram.com/365.nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4873,13 +4877,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>635</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>798</v>
+        <v>2</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4888,17 +4892,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>38752862</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/38752862</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4910,25 +4914,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>손 꽃처럼예쁘다</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>네일반짝</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>geochanggun@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1355-4142</t>
+          <t>0507-1400-7948</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40-1 지하층 B01호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_shiny_b/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4938,7 +4946,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4959,17 +4967,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="Q49" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4978,17 +4986,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1207469718</t>
+          <t>1963530909</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207469718</t>
+          <t>https://m.place.naver.com/place/1963530909</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5000,29 +5008,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일온</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dlgksmf3595@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1491-7802</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon7793</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5057,13 +5061,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>305</v>
+        <v>86</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>317</v>
+        <v>86</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5072,17 +5076,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1655818723</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655818723</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5094,29 +5098,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5151,13 +5155,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1378</v>
+        <v>556</v>
       </c>
       <c r="Q51" t="n">
-        <v>568</v>
+        <v>67</v>
       </c>
       <c r="R51" t="n">
-        <v>1946</v>
+        <v>623</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5166,17 +5170,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5188,25 +5192,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>예스네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>seo0unnienail@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1320-2494</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ye_s_nail</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5241,13 +5249,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>660</v>
+        <v>2435</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>2343</v>
       </c>
       <c r="R52" t="n">
-        <v>673</v>
+        <v>4778</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5256,17 +5264,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1073307347</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073307347</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5278,29 +5286,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>디네일</t>
+          <t>손을그리다</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>b_ye_bye@naver.com</t>
+          <t>tntpung@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1498-4179</t>
+          <t>031-704-1009</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://instagram.com/d.nail_4179</t>
+          <t>https://www.instagram.com/drawhand_nail/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5335,13 +5343,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="R53" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5350,17 +5358,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1139274960</t>
+          <t>36398915</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139274960</t>
+          <t>https://m.place.naver.com/place/36398915</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5372,34 +5380,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5420,7 +5428,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5429,13 +5437,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>107</v>
+        <v>323</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R54" t="n">
-        <v>145</v>
+        <v>356</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5444,17 +5452,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5474,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>후와네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>kimnk980409@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5523,13 +5531,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2434</v>
+        <v>447</v>
       </c>
       <c r="Q55" t="n">
-        <v>2342</v>
+        <v>18</v>
       </c>
       <c r="R55" t="n">
-        <v>4776</v>
+        <v>465</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5538,17 +5546,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5560,25 +5568,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>이브네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>그리너리프라이빗뷰티샵</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q19900320@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1405-0716</t>
+          <t>0507-1446-1041</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 16 힐스테이트엘포레6단지상가 214호</t>
+          <t>경기도 성남시 분당구 동판교로52번길 22 101호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evenail_dj_hs</t>
+          <t>https://www.instagram.com/greenery_nail/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5613,13 +5625,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="R56" t="n">
-        <v>23</v>
+        <v>306</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5628,17 +5640,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1345933789</t>
+          <t>50639356</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345933789</t>
+          <t>https://m.place.naver.com/place/50639356</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5650,25 +5662,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일드와</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>tykd2048@naver.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5703,13 +5719,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>721</v>
+        <v>443</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="R57" t="n">
-        <v>737</v>
+        <v>513</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5718,17 +5734,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5740,34 +5756,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>쏘햅삐네일</t>
+          <t>HENA BEAUTY LAB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ssohapbbi_nail@naver.com</t>
+          <t>amyloves_red@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1365-1459</t>
+          <t>0507-1419-0757</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 11 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssohapbbi_nail</t>
+          <t>http://pf.kakao.com/_zLygn</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5788,22 +5804,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>336</v>
+        <v>597</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="R58" t="n">
-        <v>342</v>
+        <v>847</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5812,17 +5828,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1699230267</t>
+          <t>30844297</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699230267</t>
+          <t>https://m.place.naver.com/place/30844297</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5834,26 +5850,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MANYONENAIL</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>디네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>b_ye_bye@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1498-4179</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 양현로 126 1층 111호</t>
+          <t>경기도 성남시 분당구 판교로 393 봇들마을2단지 이지더원아파트상가 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lzxfAn</t>
+          <t>http://instagram.com/d.nail_4179</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5874,7 +5898,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5883,13 +5907,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5898,17 +5922,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1675486546</t>
+          <t>1139274960</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675486546</t>
+          <t>https://m.place.naver.com/place/1139274960</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5920,25 +5944,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>비벨리</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>라온네일클리닉 판교 본점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1418-3314</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>https://blog.naver.com/sungunara226</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5953,7 +5981,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5973,13 +6001,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>257</v>
+        <v>67</v>
       </c>
       <c r="Q60" t="n">
-        <v>532</v>
+        <v>283</v>
       </c>
       <c r="R60" t="n">
-        <v>789</v>
+        <v>350</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5988,17 +6016,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1137420501</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1137420501</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6010,21 +6038,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일숲</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>031-603-3011</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 B2 2009호 블루존</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_soup_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6034,7 +6066,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6055,17 +6087,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="R61" t="n">
-        <v>27</v>
+        <v>334</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6074,17 +6106,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1564392316</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564392316</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6096,24 +6128,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일탐</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>kangjooho0519@naver.com</t>
-        </is>
-      </c>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1344-3330</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 103호</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6153,13 +6181,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>21</v>
+        <v>1037</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="R62" t="n">
-        <v>26</v>
+        <v>1159</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6168,17 +6196,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1400616486</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400616486</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6190,30 +6218,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>이마네일</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>네일신 판교점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>moijj@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1427-8952</t>
+          <t>031-708-4142</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트 지하2층 오렌지존 B2157호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxlBPj</t>
+          <t>https://www.instagram.com/nailshin_/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6234,7 +6266,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6243,13 +6275,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="R63" t="n">
-        <v>71</v>
+        <v>273</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6258,17 +6290,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1053041064</t>
+          <t>1768463815</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053041064</t>
+          <t>https://m.place.naver.com/place/1768463815</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6280,30 +6312,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1416-7323</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6313,7 +6349,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6333,13 +6369,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1299</v>
+        <v>66</v>
       </c>
       <c r="Q64" t="n">
-        <v>719</v>
+        <v>118</v>
       </c>
       <c r="R64" t="n">
-        <v>2018</v>
+        <v>184</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6348,17 +6384,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6370,29 +6406,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>버니스네일</t>
+          <t>손 꽃처럼예쁘다</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>saebom96@naver.com</t>
+          <t>kshkjs1225@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1381-7791</t>
+          <t>0507-1436-7943</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 430 태영건영분산상가 107호</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.suda</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6402,7 +6438,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6423,17 +6459,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="R65" t="n">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6442,17 +6478,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1103701684</t>
+          <t>37851165</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103701684</t>
+          <t>https://m.place.naver.com/place/37851165</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6464,29 +6500,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일신 판교점</t>
+          <t>로코코네일 판교본점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>moijj@naver.com</t>
+          <t>nail_rococo@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>031-708-4142</t>
+          <t>0507-1315-1583</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailshin_/</t>
+          <t>https://linktr.ee/rococonail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6512,7 +6548,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6521,13 +6557,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="Q66" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6536,17 +6572,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1768463815</t>
+          <t>1008417568</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768463815</t>
+          <t>https://m.place.naver.com/place/1008417568</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6558,25 +6594,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>코코네일</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gywjd2303@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0507-1403-3341</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6586,7 +6622,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6607,17 +6643,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1037</v>
+        <v>636</v>
       </c>
       <c r="Q67" t="n">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="R67" t="n">
-        <v>1158</v>
+        <v>799</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6626,17 +6662,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6648,25 +6684,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>031-702-8870</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6681,7 +6721,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6701,13 +6741,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>86</v>
+        <v>1382</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="R68" t="n">
-        <v>86</v>
+        <v>1950</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6716,17 +6756,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6741,11 +6781,7 @@
           <t>루미가넷 현대백화점 판교점</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>nuroonge@naver.com</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6820,7 +6856,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6832,29 +6868,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>로코코네일 판교본점</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>nail_rococo@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1315-1583</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 1층 로코코네일</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://linktr.ee/rococonail</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6869,7 +6905,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6880,7 +6916,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6889,13 +6925,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>129</v>
+        <v>1953</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>640</v>
       </c>
       <c r="R70" t="n">
-        <v>133</v>
+        <v>2593</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6904,17 +6940,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1008417568</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008417568</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6926,25 +6962,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>달래네일</t>
+          <t>네일온</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1471-1290</t>
+          <t>0507-1491-7802</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 지하1층 114-1호</t>
+          <t>경기도 성남시 분당구 운중로113번길 12-1 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dalraenail</t>
+          <t>https://www.instagram.com/nailon7793</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6979,13 +7015,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R71" t="n">
-        <v>212</v>
+        <v>317</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6994,17 +7030,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1453685923</t>
+          <t>1655818723</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453685923</t>
+          <t>https://m.place.naver.com/place/1655818723</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7016,25 +7052,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>디에고푸스 판교점 네일어베인</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>예스네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>lovmaria@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1391-8131</t>
+          <t>0507-1320-2494</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-15 지하1층, 1층</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 5층 512호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/ye_s_nail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7044,7 +7084,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7065,17 +7105,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>81</v>
+        <v>660</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R72" t="n">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7084,17 +7124,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2075785121</t>
+          <t>1073307347</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075785121</t>
+          <t>https://m.place.naver.com/place/1073307347</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7106,29 +7146,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>후와네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>kimnk980409@naver.com</t>
-        </is>
-      </c>
+          <t>바비앤네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>0507-1418-0917</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 운중로 176</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>http://barbienail.itpage.kr/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7159,17 +7195,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="R73" t="n">
-        <v>465</v>
+        <v>9</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7178,17 +7214,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>21733065</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/21733065</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7200,29 +7236,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>nailpalace@naver.com</t>
-        </is>
-      </c>
+          <t>네일드와</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 / 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7257,13 +7289,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>243</v>
+        <v>722</v>
       </c>
       <c r="Q74" t="n">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="R74" t="n">
-        <v>344</v>
+        <v>738</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7272,17 +7304,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7294,25 +7326,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>메종드리엘</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>쏘햅삐네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ssohapbbi_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1363-0109</t>
+          <t>0507-1365-1459</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로125번길 5 카페두비 반대쪽</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역오피스텔 지하2층 레드존 B2120호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ssohapbbi_nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7322,7 +7358,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7343,17 +7379,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4</v>
+        <v>336</v>
       </c>
       <c r="Q75" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="R75" t="n">
-        <v>43</v>
+        <v>342</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7362,17 +7398,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1572212961</t>
+          <t>1699230267</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572212961</t>
+          <t>https://m.place.naver.com/place/1699230267</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7384,29 +7420,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>손을그리다</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>tntpung@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>031-704-1009</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drawhand_nail/</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7441,13 +7473,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="Q76" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="R76" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7456,17 +7488,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>36398915</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36398915</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
